--- a/prompts/prompts_2026_Vasilev_Savelii.xlsx
+++ b/prompts/prompts_2026_Vasilev_Savelii.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\savelij\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{053E612F-42F3-404F-AC0B-5A3841C88CFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E0D1CAF-D9ED-4F36-A5FB-81FCFBA9F586}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="52">
   <si>
     <t>Timestamp</t>
   </si>
@@ -130,67 +130,55 @@
     <t>Анализ и визуализация данных</t>
   </si>
   <si>
-    <t>Я выполняю учебное задание по курсу Python + AI. Нужно выбрать данные из Wikidata для анализа. Я хочу сделать проект на тему: "Экономика, население и территория стран мира". Идея проекта: 1. Мини-тема 1: экономика стран. 2. Мини-тема 2: население и территория стран. 3. Объединяющая тема: связь экономического уровня страны с её населением и территорией. Мне нужны данные минимум по 50 странам и минимум 3 столбца. В данных должны быть числовые и категориальные признаки. Помоги выбрать подходящие свойства Wikidata для такого проекта и объясни, почему они подходят для анализа.</t>
-  </si>
-  <si>
-    <t>Mistral предложил свойства для анализа: население, площадь, ВВП, ВВП на душу населения, плотность населения, континент, регион и тип страны. Ответ помог выбрать направление проекта, но часть P-номеров свойств была ошибочной и потребовала проверки.</t>
-  </si>
-  <si>
-    <t>Ошибки в P-номерах свойств Wikidata</t>
-  </si>
-  <si>
-    <t>В предыдущем ответе были ошибки в свойствах Wikidata. Исправь SPARQL-запрос для темы "Экономика, население и территория стран мира". Используй такие свойства: страна: instance of country, P31 = Q6256; население: P1082; площадь: P2046; номинальный ВВП: P2131; ВВП на душу населения: P2132; континент: P30; столица: P36; валюта: P38. Нужно получить минимум 50 стран. В результате должны быть числовые и категориальные столбцы. Напиши SPARQL-запрос для Wikidata Query Service.</t>
-  </si>
-  <si>
-    <t>Mistral снова предложил запрос с ошибочными свойствами. После проверки было решено исправить SPARQL-запрос вручную и использовать правильные свойства Wikidata.</t>
-  </si>
-  <si>
-    <t>ИИ повторил неправильные свойства</t>
-  </si>
-  <si>
-    <t>ChatGPT</t>
-  </si>
-  <si>
-    <t>Проверь SPARQL-запрос для Wikidata по теме "Экономика, население и территория стран мира", исправь ошибки в свойствах и сделай так, чтобы в результате было минимум 50 стран, числовые и категориальные столбцы.</t>
-  </si>
-  <si>
-    <t>Был составлен финальный SPARQL-запрос с правильными свойствами: P1082 для населения, P2046 для площади, P2131 для ВВП, P30 для континента, P36 для столицы и P38 для валюты. Также была добавлена группировка через GROUP BY и MAX, чтобы каждая страна появлялась один раз.</t>
-  </si>
-  <si>
     <t>Нет</t>
   </si>
   <si>
     <t>Qwen AI</t>
   </si>
   <si>
-    <t>Ты — преподаватель Python для начинающих. Я выполняю задание 2 по курсу Python + AI. У меня есть GitHub-репозиторий: https://github.com/vasilevsavelij135-spec/python-ai-Vasilev-Savelii. В папке data лежит мой CSV-файл: data/countries_economy_population_area.csv. Тема проекта: "Экономика, население и территория стран мира". Мне нужно адаптировать ноутбук notebooks/week2b_read_csv.ipynb под мой CSV. Составь пошаговый план для ноутбука: какие библиотеки импортировать, как клонировать репозиторий, как прочитать CSV, как вывести первые строки, как переименовать столбцы, как привести числовые столбцы к числовому типу, как проверить пропуски и какие базовые статистики посчитать.</t>
-  </si>
-  <si>
-    <t>Qwen предложил план работы с CSV: импорт pandas, клонирование репозитория, чтение файла через pd.read_csv, просмотр первых строк, переименование столбцов, преобразование числовых данных, проверка пропусков и базовая статистика. План был использован с небольшими правками.</t>
-  </si>
-  <si>
-    <t>Помоги адаптировать week2b_read_csv.ipynb под мой датасет countries_economy_population_area.csv: прочитать CSV, переименовать столбцы, сохранить URL, привести population, area, gdp и gdp_per_capita к числам, проверить пропуски и посчитать базовую статистику.</t>
-  </si>
-  <si>
-    <t>Был подготовлен код для чтения CSV из GitHub, переименования столбцов, преобразования числовых данных, проверки пропусков и вывода базовой статистики. Ноутбук был успешно сохранён в папку notebooks.</t>
-  </si>
-  <si>
     <t>DeepSeek AI</t>
   </si>
   <si>
-    <t>Ты — преподаватель Python для начинающих. Я выполняю задание 3 по курсу Python + AI. У меня есть CSV data/countries_economy_population_area.csv по теме "Экономика, население и территория стран мира". Мне нужно адаптировать notebooks/week3_visualization.ipynb: загрузить CSV, переименовать столбцы, привести числовые столбцы к числовому типу, построить 3–4 разные визуализации и под каждым графиком написать короткий вывод. Используй pandas, matplotlib и seaborn.</t>
+    <t>Я выполняю учебное задание по курсу Python + AI. Нужно выбрать данные из Wikidata для анализа. Я хочу сделать проект на тему: "Экономика, территория, население и продолжительность жизни стран мира". Мне нужны данные минимум по 50 странам. Нужно придумать две мини-темы и одну объединяющую тему, выбрать подходящие свойства Wikidata и объяснить, почему они подходят для анализа.</t>
   </si>
   <si>
-    <t>DeepSeek предложил план визуализаций: топ стран по ВВП, scatter plot, распределение стран по континентам и boxplot ВВП на душу населения по континентам. Ответ был использован частично, но код был исправлен под реальные названия столбцов.</t>
+    <t>Mistral предложил тему, связанную с экономикой, территорией, населением и продолжительностью жизни стран мира. Были выбраны признаки для анализа стран: континент, столица, площадь, ВВП, ВВП на душу населения, население по годам и продолжительность жизни по годам.</t>
   </si>
   <si>
-    <t>Нужно было исправить названия столбцов</t>
+    <t>Составь SPARQL-запрос для основного датасета по странам мира. В запросе должны быть страна, континент, столица, площадь, ВВП, ВВП на душу населения и валюта. Не добавляй population в основной запрос. Не используй LIMIT. Сделай так, чтобы одна страна была представлена одной строкой и не было дублей из-за разных валют.</t>
   </si>
   <si>
-    <t>Проверь и улучши визуализации для моего датасета. Графики получились скучные, добавь более интересные варианты анализа.</t>
+    <t>Mistral предложил SPARQL-запрос для основного датасета. После проверки запрос был адаптирован: population убран из основного запроса, LIMIT не используется, для устранения дублей применены агрегирующие функции MAX и SAMPLE. Итоговый запрос сохранён в countries_economy_area.sparql.</t>
   </si>
   <si>
-    <t>Были добавлены дополнительные показатели: плотность населения, ВВП в триллионах и ВВП на душу населения в тысячах. Также были предложены более интересные графики: логарифмический scatter plot населения и ВВП, топ стран по ВВП на душу населения, связь плотности населения и ВВП на душу населения, средний ВВП на душу населения по континентам и корреляционная heatmap.</t>
+    <t>Добавь два отдельных SPARQL-запроса для Wikidata. Первый должен собирать по странам параметр population за все годы, представленные в Wikidata. Второй должен собирать по странам параметр life expectancy за все годы, представленные в Wikidata. Для каждого запроса нужны столбцы: страна, название страны, значение показателя и дата.</t>
+  </si>
+  <si>
+    <t>Mistral помог сформировать два дополнительных запроса. Для населения используется свойство P1082, данные сохраняются в population.sparql и population.csv. Для продолжительности жизни используется свойство P2250, данные сохраняются в life.sparql и life.csv. В обоих датасетах одна страна может повторяться несколько раз, потому что собираются значения за разные годы.</t>
+  </si>
+  <si>
+    <t>Я выполняю задание 2 по курсу Python + AI. В папке data теперь есть три CSV-файла: countries_economy_area.csv, population.csv и life.csv. Нужно адаптировать notebooks/week2b_read_csv.ipynb: прочитать все три CSV-файла, переименовать столбцы, привести числовые столбцы к числовому типу, преобразовать даты в population.csv и life.csv, проверить пропуски и посчитать базовую статистику. Составь простой пошаговый план и код для начинающего студента.</t>
+  </si>
+  <si>
+    <t>Qwen предложил структуру ноутбука для чтения трёх CSV-файлов: импорт pandas, загрузка файлов, просмотр размеров таблиц, переименование столбцов, преобразование числовых значений, обработка дат, проверка пропусков и базовая статистика.</t>
+  </si>
+  <si>
+    <t>Проверь, как лучше оформить итоговую часть ноутбука week2b_read_csv.ipynb. Нужно кратко объяснить, какие три датасета были загружены, какие преобразования выполнены и почему эти данные подходят для дальнейшего анализа.</t>
+  </si>
+  <si>
+    <t>Qwen предложил итоговый Markdown-вывод для второго ноутбука. В выводе указано, что основной файл содержит экономические и территориальные показатели стран, population.csv содержит население по годам, а life.csv содержит продолжительность жизни по годам.</t>
+  </si>
+  <si>
+    <t>Я выполняю задание 3 по курсу Python + AI. В папке data есть три CSV-файла: countries_economy_area.csv, population.csv и life.csv. Нужно адаптировать notebooks/week3_visualization.ipynb: загрузить три CSV-файла, построить визуализации по экономике стран, площади и ВВП, построить график динамики населения по годам, построить график динамики продолжительности жизни по годам, объединить экономические данные с продолжительностью жизни и написать выводы под каждым графиком. Предложи план ноутбука и код на pandas, matplotlib и seaborn.</t>
+  </si>
+  <si>
+    <t>DeepSeek предложил план визуализации для третьего задания: график топ стран по ВВП, связь площади и ВВП, средний ВВП на душу населения по континентам, динамика населения по годам, динамика продолжительности жизни и объединение экономических данных с продолжительностью жизни.</t>
+  </si>
+  <si>
+    <t>Улучши визуализации для датасетов countries_economy_area.csv, population.csv и life.csv. Нужно, чтобы графики были понятными, разными по типу и показывали связь между экономикой, территорией, населением и продолжительностью жизни. Также напиши короткие аналитические выводы под каждый график.</t>
+  </si>
+  <si>
+    <t>DeepSeek предложил улучшить графики: использовать горизонтальные столбчатые диаграммы, scatter plot в логарифмической шкале, группировку по континентам и линейные графики для динамики населения и продолжительности жизни. Эти идеи были использованы в week3_visualization.ipynb.</t>
   </si>
 </sst>
 </file>
@@ -562,7 +550,7 @@
     <col min="7" max="7" width="17.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -590,7 +578,7 @@
     </row>
     <row r="2" spans="1:8" ht="149.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="15">
-        <v>46166.583333333336</v>
+        <v>46168.777777777781</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>8</v>
@@ -602,21 +590,21 @@
         <v>9</v>
       </c>
       <c r="E2" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="6" t="s">
         <v>35</v>
-      </c>
-      <c r="F2" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="88.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="15">
-        <v>46166.590277777781</v>
+        <v>46168.78125</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>8</v>
@@ -628,21 +616,21 @@
         <v>9</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F3" s="17" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="88.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="15">
-        <v>46166.597222222219</v>
+        <v>46168.784722222219</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>8</v>
@@ -651,7 +639,7 @@
         <v>3</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="E4" s="17" t="s">
         <v>42</v>
@@ -663,111 +651,111 @@
         <v>13</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="88.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="15">
-        <v>46166.604166666664</v>
+        <v>46168.791666666664</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C5" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="F5" s="17" t="s">
         <v>45</v>
-      </c>
-      <c r="E5" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="F5" s="17" t="s">
-        <v>47</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>13</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="88.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="15">
-        <v>46166.614583333336</v>
+        <v>46168.795138888891</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C6" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>13</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="88.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="15">
-        <v>46166.631944444445</v>
+        <v>46168.802083333336</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C7" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F7" s="18" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="88.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16">
-        <v>46166.645833333336</v>
+        <v>46168.809027777781</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>33</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G8" s="9" t="s">
         <v>13</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="88.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -776,5947 +764,5947 @@
       <c r="G9" s="9"/>
       <c r="H9" s="6"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B10" s="7"/>
       <c r="D10" s="8"/>
       <c r="G10" s="9"/>
       <c r="H10" s="6"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B11" s="7"/>
       <c r="D11" s="8"/>
       <c r="G11" s="9"/>
       <c r="H11" s="6"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B12" s="7"/>
       <c r="D12" s="8"/>
       <c r="G12" s="9"/>
       <c r="H12" s="6"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B13" s="7"/>
       <c r="D13" s="8"/>
       <c r="G13" s="9"/>
       <c r="H13" s="6"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B14" s="7"/>
       <c r="D14" s="8"/>
       <c r="G14" s="9"/>
       <c r="H14" s="6"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B15" s="7"/>
       <c r="D15" s="8"/>
       <c r="G15" s="9"/>
       <c r="H15" s="6"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B16" s="7"/>
       <c r="D16" s="8"/>
       <c r="G16" s="9"/>
       <c r="H16" s="6"/>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B17" s="7"/>
       <c r="D17" s="8"/>
       <c r="G17" s="9"/>
       <c r="H17" s="6"/>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B18" s="7"/>
       <c r="D18" s="8"/>
       <c r="G18" s="9"/>
       <c r="H18" s="6"/>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B19" s="7"/>
       <c r="D19" s="8"/>
       <c r="G19" s="9"/>
       <c r="H19" s="6"/>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B20" s="7"/>
       <c r="D20" s="8"/>
       <c r="G20" s="9"/>
       <c r="H20" s="6"/>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B21" s="7"/>
       <c r="D21" s="8"/>
       <c r="G21" s="9"/>
       <c r="H21" s="6"/>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B22" s="7"/>
       <c r="D22" s="8"/>
       <c r="G22" s="9"/>
       <c r="H22" s="6"/>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B23" s="7"/>
       <c r="D23" s="8"/>
       <c r="G23" s="9"/>
       <c r="H23" s="6"/>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B24" s="7"/>
       <c r="D24" s="8"/>
       <c r="G24" s="9"/>
       <c r="H24" s="6"/>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B25" s="7"/>
       <c r="D25" s="8"/>
       <c r="G25" s="9"/>
       <c r="H25" s="6"/>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B26" s="7"/>
       <c r="D26" s="8"/>
       <c r="G26" s="9"/>
       <c r="H26" s="6"/>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B27" s="7"/>
       <c r="D27" s="8"/>
       <c r="G27" s="9"/>
       <c r="H27" s="6"/>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B28" s="7"/>
       <c r="D28" s="8"/>
       <c r="G28" s="9"/>
       <c r="H28" s="6"/>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B29" s="7"/>
       <c r="D29" s="8"/>
       <c r="G29" s="9"/>
       <c r="H29" s="6"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B30" s="7"/>
       <c r="D30" s="8"/>
       <c r="G30" s="9"/>
       <c r="H30" s="6"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B31" s="7"/>
       <c r="D31" s="8"/>
       <c r="G31" s="9"/>
       <c r="H31" s="6"/>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B32" s="7"/>
       <c r="D32" s="8"/>
       <c r="G32" s="9"/>
       <c r="H32" s="6"/>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B33" s="7"/>
       <c r="D33" s="8"/>
       <c r="G33" s="9"/>
       <c r="H33" s="6"/>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B34" s="7"/>
       <c r="D34" s="8"/>
       <c r="G34" s="9"/>
       <c r="H34" s="6"/>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B35" s="7"/>
       <c r="D35" s="8"/>
       <c r="G35" s="9"/>
       <c r="H35" s="6"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B36" s="7"/>
       <c r="D36" s="8"/>
       <c r="G36" s="9"/>
       <c r="H36" s="6"/>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B37" s="7"/>
       <c r="D37" s="8"/>
       <c r="G37" s="9"/>
       <c r="H37" s="6"/>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B38" s="7"/>
       <c r="D38" s="8"/>
       <c r="G38" s="9"/>
       <c r="H38" s="6"/>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B39" s="7"/>
       <c r="D39" s="8"/>
       <c r="G39" s="9"/>
       <c r="H39" s="6"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B40" s="7"/>
       <c r="D40" s="8"/>
       <c r="G40" s="9"/>
       <c r="H40" s="6"/>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B41" s="7"/>
       <c r="D41" s="8"/>
       <c r="G41" s="9"/>
       <c r="H41" s="6"/>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B42" s="7"/>
       <c r="D42" s="8"/>
       <c r="G42" s="9"/>
       <c r="H42" s="6"/>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B43" s="7"/>
       <c r="D43" s="8"/>
       <c r="G43" s="9"/>
       <c r="H43" s="6"/>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B44" s="7"/>
       <c r="D44" s="8"/>
       <c r="G44" s="9"/>
       <c r="H44" s="6"/>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B45" s="7"/>
       <c r="D45" s="8"/>
       <c r="G45" s="9"/>
       <c r="H45" s="6"/>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B46" s="7"/>
       <c r="D46" s="8"/>
       <c r="G46" s="9"/>
       <c r="H46" s="6"/>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B47" s="7"/>
       <c r="D47" s="8"/>
       <c r="G47" s="9"/>
       <c r="H47" s="6"/>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B48" s="7"/>
       <c r="D48" s="8"/>
       <c r="G48" s="9"/>
       <c r="H48" s="6"/>
     </row>
-    <row r="49" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B49" s="7"/>
       <c r="D49" s="8"/>
       <c r="G49" s="9"/>
       <c r="H49" s="6"/>
     </row>
-    <row r="50" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B50" s="7"/>
       <c r="D50" s="8"/>
       <c r="G50" s="9"/>
       <c r="H50" s="6"/>
     </row>
-    <row r="51" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B51" s="7"/>
       <c r="D51" s="8"/>
       <c r="G51" s="9"/>
       <c r="H51" s="6"/>
     </row>
-    <row r="52" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B52" s="7"/>
       <c r="D52" s="8"/>
       <c r="G52" s="9"/>
       <c r="H52" s="6"/>
     </row>
-    <row r="53" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B53" s="7"/>
       <c r="D53" s="8"/>
       <c r="G53" s="9"/>
       <c r="H53" s="6"/>
     </row>
-    <row r="54" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B54" s="7"/>
       <c r="D54" s="8"/>
       <c r="G54" s="9"/>
       <c r="H54" s="6"/>
     </row>
-    <row r="55" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B55" s="7"/>
       <c r="D55" s="8"/>
       <c r="G55" s="9"/>
       <c r="H55" s="6"/>
     </row>
-    <row r="56" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B56" s="7"/>
       <c r="D56" s="8"/>
       <c r="G56" s="9"/>
       <c r="H56" s="6"/>
     </row>
-    <row r="57" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B57" s="7"/>
       <c r="D57" s="8"/>
       <c r="G57" s="9"/>
       <c r="H57" s="6"/>
     </row>
-    <row r="58" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B58" s="7"/>
       <c r="D58" s="8"/>
       <c r="G58" s="9"/>
       <c r="H58" s="6"/>
     </row>
-    <row r="59" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B59" s="7"/>
       <c r="D59" s="8"/>
       <c r="G59" s="9"/>
       <c r="H59" s="6"/>
     </row>
-    <row r="60" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B60" s="7"/>
       <c r="D60" s="8"/>
       <c r="G60" s="9"/>
       <c r="H60" s="6"/>
     </row>
-    <row r="61" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B61" s="7"/>
       <c r="D61" s="8"/>
       <c r="G61" s="9"/>
       <c r="H61" s="6"/>
     </row>
-    <row r="62" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B62" s="7"/>
       <c r="D62" s="8"/>
       <c r="G62" s="9"/>
       <c r="H62" s="6"/>
     </row>
-    <row r="63" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B63" s="7"/>
       <c r="D63" s="8"/>
       <c r="G63" s="9"/>
       <c r="H63" s="6"/>
     </row>
-    <row r="64" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B64" s="7"/>
       <c r="D64" s="8"/>
       <c r="G64" s="9"/>
       <c r="H64" s="6"/>
     </row>
-    <row r="65" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B65" s="7"/>
       <c r="D65" s="8"/>
       <c r="G65" s="9"/>
       <c r="H65" s="6"/>
     </row>
-    <row r="66" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B66" s="7"/>
       <c r="D66" s="8"/>
       <c r="G66" s="9"/>
       <c r="H66" s="6"/>
     </row>
-    <row r="67" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B67" s="7"/>
       <c r="D67" s="8"/>
       <c r="G67" s="9"/>
       <c r="H67" s="6"/>
     </row>
-    <row r="68" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B68" s="7"/>
       <c r="D68" s="8"/>
       <c r="G68" s="9"/>
       <c r="H68" s="6"/>
     </row>
-    <row r="69" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B69" s="7"/>
       <c r="D69" s="8"/>
       <c r="G69" s="9"/>
       <c r="H69" s="6"/>
     </row>
-    <row r="70" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B70" s="7"/>
       <c r="D70" s="8"/>
       <c r="G70" s="9"/>
       <c r="H70" s="6"/>
     </row>
-    <row r="71" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B71" s="7"/>
       <c r="D71" s="8"/>
       <c r="G71" s="9"/>
       <c r="H71" s="6"/>
     </row>
-    <row r="72" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B72" s="7"/>
       <c r="D72" s="8"/>
       <c r="G72" s="9"/>
       <c r="H72" s="6"/>
     </row>
-    <row r="73" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B73" s="7"/>
       <c r="D73" s="8"/>
       <c r="G73" s="9"/>
       <c r="H73" s="6"/>
     </row>
-    <row r="74" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B74" s="7"/>
       <c r="D74" s="8"/>
       <c r="G74" s="9"/>
       <c r="H74" s="6"/>
     </row>
-    <row r="75" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B75" s="7"/>
       <c r="D75" s="8"/>
       <c r="G75" s="9"/>
       <c r="H75" s="6"/>
     </row>
-    <row r="76" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B76" s="7"/>
       <c r="D76" s="8"/>
       <c r="G76" s="9"/>
       <c r="H76" s="6"/>
     </row>
-    <row r="77" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B77" s="7"/>
       <c r="D77" s="8"/>
       <c r="G77" s="9"/>
       <c r="H77" s="6"/>
     </row>
-    <row r="78" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B78" s="7"/>
       <c r="D78" s="8"/>
       <c r="G78" s="9"/>
       <c r="H78" s="6"/>
     </row>
-    <row r="79" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B79" s="7"/>
       <c r="D79" s="8"/>
       <c r="G79" s="9"/>
       <c r="H79" s="6"/>
     </row>
-    <row r="80" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B80" s="7"/>
       <c r="D80" s="8"/>
       <c r="G80" s="9"/>
       <c r="H80" s="6"/>
     </row>
-    <row r="81" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B81" s="7"/>
       <c r="D81" s="8"/>
       <c r="G81" s="9"/>
       <c r="H81" s="6"/>
     </row>
-    <row r="82" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B82" s="7"/>
       <c r="D82" s="8"/>
       <c r="G82" s="9"/>
       <c r="H82" s="6"/>
     </row>
-    <row r="83" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B83" s="7"/>
       <c r="D83" s="8"/>
       <c r="G83" s="9"/>
       <c r="H83" s="6"/>
     </row>
-    <row r="84" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B84" s="7"/>
       <c r="D84" s="8"/>
       <c r="G84" s="9"/>
       <c r="H84" s="6"/>
     </row>
-    <row r="85" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B85" s="7"/>
       <c r="D85" s="8"/>
       <c r="G85" s="9"/>
       <c r="H85" s="6"/>
     </row>
-    <row r="86" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B86" s="7"/>
       <c r="D86" s="8"/>
       <c r="G86" s="9"/>
       <c r="H86" s="6"/>
     </row>
-    <row r="87" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B87" s="7"/>
       <c r="D87" s="8"/>
       <c r="G87" s="9"/>
       <c r="H87" s="6"/>
     </row>
-    <row r="88" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B88" s="7"/>
       <c r="D88" s="8"/>
       <c r="G88" s="9"/>
       <c r="H88" s="6"/>
     </row>
-    <row r="89" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B89" s="7"/>
       <c r="D89" s="8"/>
       <c r="G89" s="9"/>
       <c r="H89" s="6"/>
     </row>
-    <row r="90" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B90" s="7"/>
       <c r="D90" s="8"/>
       <c r="G90" s="9"/>
       <c r="H90" s="6"/>
     </row>
-    <row r="91" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B91" s="7"/>
       <c r="D91" s="8"/>
       <c r="G91" s="9"/>
       <c r="H91" s="6"/>
     </row>
-    <row r="92" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B92" s="7"/>
       <c r="D92" s="8"/>
       <c r="G92" s="9"/>
       <c r="H92" s="6"/>
     </row>
-    <row r="93" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B93" s="7"/>
       <c r="D93" s="8"/>
       <c r="G93" s="9"/>
       <c r="H93" s="6"/>
     </row>
-    <row r="94" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B94" s="7"/>
       <c r="D94" s="8"/>
       <c r="G94" s="9"/>
       <c r="H94" s="6"/>
     </row>
-    <row r="95" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B95" s="7"/>
       <c r="D95" s="8"/>
       <c r="G95" s="9"/>
       <c r="H95" s="6"/>
     </row>
-    <row r="96" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B96" s="7"/>
       <c r="D96" s="8"/>
       <c r="G96" s="9"/>
       <c r="H96" s="6"/>
     </row>
-    <row r="97" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B97" s="7"/>
       <c r="D97" s="8"/>
       <c r="G97" s="9"/>
       <c r="H97" s="6"/>
     </row>
-    <row r="98" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B98" s="7"/>
       <c r="D98" s="8"/>
       <c r="G98" s="9"/>
       <c r="H98" s="6"/>
     </row>
-    <row r="99" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B99" s="7"/>
       <c r="D99" s="8"/>
       <c r="G99" s="9"/>
       <c r="H99" s="6"/>
     </row>
-    <row r="100" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B100" s="7"/>
       <c r="D100" s="8"/>
       <c r="G100" s="9"/>
       <c r="H100" s="6"/>
     </row>
-    <row r="101" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B101" s="7"/>
       <c r="D101" s="8"/>
       <c r="G101" s="9"/>
       <c r="H101" s="6"/>
     </row>
-    <row r="102" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B102" s="7"/>
       <c r="D102" s="8"/>
       <c r="G102" s="9"/>
       <c r="H102" s="6"/>
     </row>
-    <row r="103" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B103" s="7"/>
       <c r="D103" s="8"/>
       <c r="G103" s="9"/>
       <c r="H103" s="6"/>
     </row>
-    <row r="104" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B104" s="7"/>
       <c r="D104" s="8"/>
       <c r="G104" s="9"/>
       <c r="H104" s="6"/>
     </row>
-    <row r="105" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B105" s="7"/>
       <c r="D105" s="8"/>
       <c r="G105" s="9"/>
       <c r="H105" s="6"/>
     </row>
-    <row r="106" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B106" s="7"/>
       <c r="D106" s="8"/>
       <c r="G106" s="9"/>
       <c r="H106" s="6"/>
     </row>
-    <row r="107" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B107" s="7"/>
       <c r="D107" s="8"/>
       <c r="G107" s="9"/>
       <c r="H107" s="6"/>
     </row>
-    <row r="108" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B108" s="7"/>
       <c r="D108" s="8"/>
       <c r="G108" s="9"/>
       <c r="H108" s="6"/>
     </row>
-    <row r="109" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B109" s="7"/>
       <c r="D109" s="8"/>
       <c r="G109" s="9"/>
       <c r="H109" s="6"/>
     </row>
-    <row r="110" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B110" s="7"/>
       <c r="D110" s="8"/>
       <c r="G110" s="9"/>
       <c r="H110" s="6"/>
     </row>
-    <row r="111" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B111" s="7"/>
       <c r="D111" s="8"/>
       <c r="G111" s="9"/>
       <c r="H111" s="6"/>
     </row>
-    <row r="112" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B112" s="7"/>
       <c r="D112" s="8"/>
       <c r="G112" s="9"/>
       <c r="H112" s="6"/>
     </row>
-    <row r="113" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B113" s="7"/>
       <c r="D113" s="8"/>
       <c r="G113" s="9"/>
       <c r="H113" s="6"/>
     </row>
-    <row r="114" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B114" s="7"/>
       <c r="D114" s="8"/>
       <c r="G114" s="9"/>
       <c r="H114" s="6"/>
     </row>
-    <row r="115" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B115" s="7"/>
       <c r="D115" s="8"/>
       <c r="G115" s="9"/>
       <c r="H115" s="6"/>
     </row>
-    <row r="116" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B116" s="7"/>
       <c r="D116" s="8"/>
       <c r="G116" s="9"/>
       <c r="H116" s="6"/>
     </row>
-    <row r="117" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B117" s="7"/>
       <c r="D117" s="8"/>
       <c r="G117" s="9"/>
       <c r="H117" s="6"/>
     </row>
-    <row r="118" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B118" s="7"/>
       <c r="D118" s="8"/>
       <c r="G118" s="9"/>
       <c r="H118" s="6"/>
     </row>
-    <row r="119" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B119" s="7"/>
       <c r="D119" s="8"/>
       <c r="G119" s="9"/>
       <c r="H119" s="6"/>
     </row>
-    <row r="120" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B120" s="7"/>
       <c r="D120" s="8"/>
       <c r="G120" s="9"/>
       <c r="H120" s="6"/>
     </row>
-    <row r="121" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B121" s="7"/>
       <c r="D121" s="8"/>
       <c r="G121" s="9"/>
       <c r="H121" s="6"/>
     </row>
-    <row r="122" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B122" s="7"/>
       <c r="D122" s="8"/>
       <c r="G122" s="9"/>
       <c r="H122" s="6"/>
     </row>
-    <row r="123" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B123" s="7"/>
       <c r="D123" s="8"/>
       <c r="G123" s="9"/>
       <c r="H123" s="6"/>
     </row>
-    <row r="124" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B124" s="7"/>
       <c r="D124" s="8"/>
       <c r="G124" s="9"/>
       <c r="H124" s="6"/>
     </row>
-    <row r="125" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B125" s="7"/>
       <c r="D125" s="8"/>
       <c r="G125" s="9"/>
       <c r="H125" s="6"/>
     </row>
-    <row r="126" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B126" s="7"/>
       <c r="D126" s="8"/>
       <c r="G126" s="9"/>
       <c r="H126" s="6"/>
     </row>
-    <row r="127" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B127" s="7"/>
       <c r="D127" s="8"/>
       <c r="G127" s="9"/>
       <c r="H127" s="6"/>
     </row>
-    <row r="128" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B128" s="7"/>
       <c r="D128" s="8"/>
       <c r="G128" s="9"/>
       <c r="H128" s="6"/>
     </row>
-    <row r="129" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="129" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B129" s="7"/>
       <c r="D129" s="8"/>
       <c r="G129" s="9"/>
       <c r="H129" s="6"/>
     </row>
-    <row r="130" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="130" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B130" s="7"/>
       <c r="D130" s="8"/>
       <c r="G130" s="9"/>
       <c r="H130" s="6"/>
     </row>
-    <row r="131" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="131" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B131" s="7"/>
       <c r="D131" s="8"/>
       <c r="G131" s="9"/>
       <c r="H131" s="6"/>
     </row>
-    <row r="132" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="132" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B132" s="7"/>
       <c r="D132" s="8"/>
       <c r="G132" s="9"/>
       <c r="H132" s="6"/>
     </row>
-    <row r="133" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="133" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B133" s="7"/>
       <c r="D133" s="8"/>
       <c r="G133" s="9"/>
       <c r="H133" s="6"/>
     </row>
-    <row r="134" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="134" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B134" s="7"/>
       <c r="D134" s="8"/>
       <c r="G134" s="9"/>
       <c r="H134" s="6"/>
     </row>
-    <row r="135" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="135" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B135" s="7"/>
       <c r="D135" s="8"/>
       <c r="G135" s="9"/>
       <c r="H135" s="6"/>
     </row>
-    <row r="136" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="136" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B136" s="7"/>
       <c r="D136" s="8"/>
       <c r="G136" s="9"/>
       <c r="H136" s="6"/>
     </row>
-    <row r="137" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="137" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B137" s="7"/>
       <c r="D137" s="8"/>
       <c r="G137" s="9"/>
       <c r="H137" s="6"/>
     </row>
-    <row r="138" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="138" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B138" s="7"/>
       <c r="D138" s="8"/>
       <c r="G138" s="9"/>
       <c r="H138" s="6"/>
     </row>
-    <row r="139" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="139" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B139" s="7"/>
       <c r="D139" s="8"/>
       <c r="G139" s="9"/>
       <c r="H139" s="6"/>
     </row>
-    <row r="140" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="140" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B140" s="7"/>
       <c r="D140" s="8"/>
       <c r="G140" s="9"/>
       <c r="H140" s="6"/>
     </row>
-    <row r="141" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="141" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B141" s="7"/>
       <c r="D141" s="8"/>
       <c r="G141" s="9"/>
       <c r="H141" s="6"/>
     </row>
-    <row r="142" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="142" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B142" s="7"/>
       <c r="D142" s="8"/>
       <c r="G142" s="9"/>
       <c r="H142" s="6"/>
     </row>
-    <row r="143" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="143" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B143" s="7"/>
       <c r="D143" s="8"/>
       <c r="G143" s="9"/>
       <c r="H143" s="6"/>
     </row>
-    <row r="144" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="144" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B144" s="7"/>
       <c r="D144" s="8"/>
       <c r="G144" s="9"/>
       <c r="H144" s="6"/>
     </row>
-    <row r="145" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="145" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B145" s="7"/>
       <c r="D145" s="8"/>
       <c r="G145" s="9"/>
       <c r="H145" s="6"/>
     </row>
-    <row r="146" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="146" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B146" s="7"/>
       <c r="D146" s="8"/>
       <c r="G146" s="9"/>
       <c r="H146" s="6"/>
     </row>
-    <row r="147" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="147" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B147" s="7"/>
       <c r="D147" s="8"/>
       <c r="G147" s="9"/>
       <c r="H147" s="6"/>
     </row>
-    <row r="148" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="148" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B148" s="7"/>
       <c r="D148" s="8"/>
       <c r="G148" s="9"/>
       <c r="H148" s="6"/>
     </row>
-    <row r="149" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="149" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B149" s="7"/>
       <c r="D149" s="8"/>
       <c r="G149" s="9"/>
       <c r="H149" s="6"/>
     </row>
-    <row r="150" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="150" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B150" s="7"/>
       <c r="D150" s="8"/>
       <c r="G150" s="9"/>
       <c r="H150" s="6"/>
     </row>
-    <row r="151" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="151" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B151" s="7"/>
       <c r="D151" s="8"/>
       <c r="G151" s="9"/>
       <c r="H151" s="6"/>
     </row>
-    <row r="152" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="152" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B152" s="7"/>
       <c r="D152" s="8"/>
       <c r="G152" s="9"/>
       <c r="H152" s="6"/>
     </row>
-    <row r="153" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="153" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B153" s="7"/>
       <c r="D153" s="8"/>
       <c r="G153" s="9"/>
       <c r="H153" s="6"/>
     </row>
-    <row r="154" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="154" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B154" s="7"/>
       <c r="D154" s="8"/>
       <c r="G154" s="9"/>
       <c r="H154" s="6"/>
     </row>
-    <row r="155" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="155" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B155" s="7"/>
       <c r="D155" s="8"/>
       <c r="G155" s="9"/>
       <c r="H155" s="6"/>
     </row>
-    <row r="156" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="156" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B156" s="7"/>
       <c r="D156" s="8"/>
       <c r="G156" s="9"/>
       <c r="H156" s="6"/>
     </row>
-    <row r="157" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="157" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B157" s="7"/>
       <c r="D157" s="8"/>
       <c r="G157" s="9"/>
       <c r="H157" s="6"/>
     </row>
-    <row r="158" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="158" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B158" s="7"/>
       <c r="D158" s="8"/>
       <c r="G158" s="9"/>
       <c r="H158" s="6"/>
     </row>
-    <row r="159" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="159" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B159" s="7"/>
       <c r="D159" s="8"/>
       <c r="G159" s="9"/>
       <c r="H159" s="6"/>
     </row>
-    <row r="160" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="160" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B160" s="7"/>
       <c r="D160" s="8"/>
       <c r="G160" s="9"/>
       <c r="H160" s="6"/>
     </row>
-    <row r="161" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="161" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B161" s="7"/>
       <c r="D161" s="8"/>
       <c r="G161" s="9"/>
       <c r="H161" s="6"/>
     </row>
-    <row r="162" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="162" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B162" s="7"/>
       <c r="D162" s="8"/>
       <c r="G162" s="9"/>
       <c r="H162" s="6"/>
     </row>
-    <row r="163" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="163" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B163" s="7"/>
       <c r="D163" s="8"/>
       <c r="G163" s="9"/>
       <c r="H163" s="6"/>
     </row>
-    <row r="164" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="164" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B164" s="7"/>
       <c r="D164" s="8"/>
       <c r="G164" s="9"/>
       <c r="H164" s="6"/>
     </row>
-    <row r="165" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="165" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B165" s="7"/>
       <c r="D165" s="8"/>
       <c r="G165" s="9"/>
       <c r="H165" s="6"/>
     </row>
-    <row r="166" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="166" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B166" s="7"/>
       <c r="D166" s="8"/>
       <c r="G166" s="9"/>
       <c r="H166" s="6"/>
     </row>
-    <row r="167" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="167" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B167" s="7"/>
       <c r="D167" s="8"/>
       <c r="G167" s="9"/>
       <c r="H167" s="6"/>
     </row>
-    <row r="168" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="168" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B168" s="7"/>
       <c r="D168" s="8"/>
       <c r="G168" s="9"/>
       <c r="H168" s="6"/>
     </row>
-    <row r="169" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="169" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B169" s="7"/>
       <c r="D169" s="8"/>
       <c r="G169" s="9"/>
       <c r="H169" s="6"/>
     </row>
-    <row r="170" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="170" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B170" s="7"/>
       <c r="D170" s="8"/>
       <c r="G170" s="9"/>
       <c r="H170" s="6"/>
     </row>
-    <row r="171" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="171" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B171" s="7"/>
       <c r="D171" s="8"/>
       <c r="G171" s="9"/>
       <c r="H171" s="6"/>
     </row>
-    <row r="172" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="172" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B172" s="7"/>
       <c r="D172" s="8"/>
       <c r="G172" s="9"/>
       <c r="H172" s="6"/>
     </row>
-    <row r="173" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="173" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B173" s="7"/>
       <c r="D173" s="8"/>
       <c r="G173" s="9"/>
       <c r="H173" s="6"/>
     </row>
-    <row r="174" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B174" s="7"/>
       <c r="D174" s="8"/>
       <c r="G174" s="9"/>
       <c r="H174" s="6"/>
     </row>
-    <row r="175" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="175" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B175" s="7"/>
       <c r="D175" s="8"/>
       <c r="G175" s="9"/>
       <c r="H175" s="6"/>
     </row>
-    <row r="176" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="176" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B176" s="7"/>
       <c r="D176" s="8"/>
       <c r="G176" s="9"/>
       <c r="H176" s="6"/>
     </row>
-    <row r="177" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="177" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B177" s="7"/>
       <c r="D177" s="8"/>
       <c r="G177" s="9"/>
       <c r="H177" s="6"/>
     </row>
-    <row r="178" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="178" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B178" s="7"/>
       <c r="D178" s="8"/>
       <c r="G178" s="9"/>
       <c r="H178" s="6"/>
     </row>
-    <row r="179" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B179" s="7"/>
       <c r="D179" s="8"/>
       <c r="G179" s="9"/>
       <c r="H179" s="6"/>
     </row>
-    <row r="180" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="180" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B180" s="7"/>
       <c r="D180" s="8"/>
       <c r="G180" s="9"/>
       <c r="H180" s="6"/>
     </row>
-    <row r="181" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="181" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B181" s="7"/>
       <c r="D181" s="8"/>
       <c r="G181" s="9"/>
       <c r="H181" s="6"/>
     </row>
-    <row r="182" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="182" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B182" s="7"/>
       <c r="D182" s="8"/>
       <c r="G182" s="9"/>
       <c r="H182" s="6"/>
     </row>
-    <row r="183" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="183" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B183" s="7"/>
       <c r="D183" s="8"/>
       <c r="G183" s="9"/>
       <c r="H183" s="6"/>
     </row>
-    <row r="184" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="184" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B184" s="7"/>
       <c r="D184" s="8"/>
       <c r="G184" s="9"/>
       <c r="H184" s="6"/>
     </row>
-    <row r="185" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="185" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B185" s="7"/>
       <c r="D185" s="8"/>
       <c r="G185" s="9"/>
       <c r="H185" s="6"/>
     </row>
-    <row r="186" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="186" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B186" s="7"/>
       <c r="D186" s="8"/>
       <c r="G186" s="9"/>
       <c r="H186" s="6"/>
     </row>
-    <row r="187" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="187" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B187" s="7"/>
       <c r="D187" s="8"/>
       <c r="G187" s="9"/>
       <c r="H187" s="6"/>
     </row>
-    <row r="188" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="188" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B188" s="7"/>
       <c r="D188" s="8"/>
       <c r="G188" s="9"/>
       <c r="H188" s="6"/>
     </row>
-    <row r="189" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B189" s="7"/>
       <c r="D189" s="8"/>
       <c r="G189" s="9"/>
       <c r="H189" s="6"/>
     </row>
-    <row r="190" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="190" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B190" s="7"/>
       <c r="D190" s="8"/>
       <c r="G190" s="9"/>
       <c r="H190" s="6"/>
     </row>
-    <row r="191" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="191" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B191" s="7"/>
       <c r="D191" s="8"/>
       <c r="G191" s="9"/>
       <c r="H191" s="6"/>
     </row>
-    <row r="192" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="192" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B192" s="7"/>
       <c r="D192" s="8"/>
       <c r="G192" s="9"/>
       <c r="H192" s="6"/>
     </row>
-    <row r="193" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="193" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B193" s="7"/>
       <c r="D193" s="8"/>
       <c r="G193" s="9"/>
       <c r="H193" s="6"/>
     </row>
-    <row r="194" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="194" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B194" s="7"/>
       <c r="D194" s="8"/>
       <c r="G194" s="9"/>
       <c r="H194" s="6"/>
     </row>
-    <row r="195" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="195" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B195" s="7"/>
       <c r="D195" s="8"/>
       <c r="G195" s="9"/>
       <c r="H195" s="6"/>
     </row>
-    <row r="196" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="196" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B196" s="7"/>
       <c r="D196" s="8"/>
       <c r="G196" s="9"/>
       <c r="H196" s="6"/>
     </row>
-    <row r="197" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="197" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B197" s="7"/>
       <c r="D197" s="8"/>
       <c r="G197" s="9"/>
       <c r="H197" s="6"/>
     </row>
-    <row r="198" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="198" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B198" s="7"/>
       <c r="D198" s="8"/>
       <c r="G198" s="9"/>
       <c r="H198" s="6"/>
     </row>
-    <row r="199" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="199" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B199" s="7"/>
       <c r="D199" s="8"/>
       <c r="G199" s="9"/>
       <c r="H199" s="6"/>
     </row>
-    <row r="200" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="200" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B200" s="7"/>
       <c r="D200" s="8"/>
       <c r="G200" s="9"/>
       <c r="H200" s="6"/>
     </row>
-    <row r="201" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="201" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B201" s="7"/>
       <c r="D201" s="8"/>
       <c r="G201" s="9"/>
       <c r="H201" s="6"/>
     </row>
-    <row r="202" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="202" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B202" s="7"/>
       <c r="D202" s="8"/>
       <c r="G202" s="9"/>
       <c r="H202" s="6"/>
     </row>
-    <row r="203" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="203" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B203" s="7"/>
       <c r="D203" s="8"/>
       <c r="G203" s="9"/>
       <c r="H203" s="6"/>
     </row>
-    <row r="204" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="204" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B204" s="7"/>
       <c r="D204" s="8"/>
       <c r="G204" s="9"/>
       <c r="H204" s="6"/>
     </row>
-    <row r="205" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="205" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B205" s="7"/>
       <c r="D205" s="8"/>
       <c r="G205" s="9"/>
       <c r="H205" s="6"/>
     </row>
-    <row r="206" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="206" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B206" s="7"/>
       <c r="D206" s="8"/>
       <c r="G206" s="9"/>
       <c r="H206" s="6"/>
     </row>
-    <row r="207" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="207" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B207" s="7"/>
       <c r="D207" s="8"/>
       <c r="G207" s="9"/>
       <c r="H207" s="6"/>
     </row>
-    <row r="208" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="208" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B208" s="7"/>
       <c r="D208" s="8"/>
       <c r="G208" s="9"/>
       <c r="H208" s="6"/>
     </row>
-    <row r="209" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="209" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B209" s="7"/>
       <c r="D209" s="8"/>
       <c r="G209" s="9"/>
       <c r="H209" s="6"/>
     </row>
-    <row r="210" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="210" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B210" s="7"/>
       <c r="D210" s="8"/>
       <c r="G210" s="9"/>
       <c r="H210" s="6"/>
     </row>
-    <row r="211" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="211" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B211" s="7"/>
       <c r="D211" s="8"/>
       <c r="G211" s="9"/>
       <c r="H211" s="6"/>
     </row>
-    <row r="212" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="212" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B212" s="7"/>
       <c r="D212" s="8"/>
       <c r="G212" s="9"/>
       <c r="H212" s="6"/>
     </row>
-    <row r="213" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="213" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B213" s="7"/>
       <c r="D213" s="8"/>
       <c r="G213" s="9"/>
       <c r="H213" s="6"/>
     </row>
-    <row r="214" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="214" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B214" s="7"/>
       <c r="D214" s="8"/>
       <c r="G214" s="9"/>
       <c r="H214" s="6"/>
     </row>
-    <row r="215" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="215" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B215" s="7"/>
       <c r="D215" s="8"/>
       <c r="G215" s="9"/>
       <c r="H215" s="6"/>
     </row>
-    <row r="216" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="216" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B216" s="7"/>
       <c r="D216" s="8"/>
       <c r="G216" s="9"/>
       <c r="H216" s="6"/>
     </row>
-    <row r="217" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="217" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B217" s="7"/>
       <c r="D217" s="8"/>
       <c r="G217" s="9"/>
       <c r="H217" s="6"/>
     </row>
-    <row r="218" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="218" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B218" s="7"/>
       <c r="D218" s="8"/>
       <c r="G218" s="9"/>
       <c r="H218" s="6"/>
     </row>
-    <row r="219" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="219" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B219" s="7"/>
       <c r="D219" s="8"/>
       <c r="G219" s="9"/>
       <c r="H219" s="6"/>
     </row>
-    <row r="220" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="220" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B220" s="7"/>
       <c r="D220" s="8"/>
       <c r="G220" s="9"/>
       <c r="H220" s="6"/>
     </row>
-    <row r="221" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="221" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B221" s="7"/>
       <c r="D221" s="8"/>
       <c r="G221" s="9"/>
       <c r="H221" s="6"/>
     </row>
-    <row r="222" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="222" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B222" s="7"/>
       <c r="D222" s="8"/>
       <c r="G222" s="9"/>
       <c r="H222" s="6"/>
     </row>
-    <row r="223" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="223" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B223" s="7"/>
       <c r="D223" s="8"/>
       <c r="G223" s="9"/>
       <c r="H223" s="6"/>
     </row>
-    <row r="224" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="224" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B224" s="7"/>
       <c r="D224" s="8"/>
       <c r="G224" s="9"/>
       <c r="H224" s="6"/>
     </row>
-    <row r="225" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="225" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B225" s="7"/>
       <c r="D225" s="8"/>
       <c r="G225" s="9"/>
       <c r="H225" s="6"/>
     </row>
-    <row r="226" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="226" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B226" s="7"/>
       <c r="D226" s="8"/>
       <c r="G226" s="9"/>
       <c r="H226" s="6"/>
     </row>
-    <row r="227" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="227" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B227" s="7"/>
       <c r="D227" s="8"/>
       <c r="G227" s="9"/>
       <c r="H227" s="6"/>
     </row>
-    <row r="228" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="228" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B228" s="7"/>
       <c r="D228" s="8"/>
       <c r="G228" s="9"/>
       <c r="H228" s="6"/>
     </row>
-    <row r="229" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="229" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B229" s="7"/>
       <c r="D229" s="8"/>
       <c r="G229" s="9"/>
       <c r="H229" s="6"/>
     </row>
-    <row r="230" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="230" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B230" s="7"/>
       <c r="D230" s="8"/>
       <c r="G230" s="9"/>
       <c r="H230" s="6"/>
     </row>
-    <row r="231" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="231" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B231" s="7"/>
       <c r="D231" s="8"/>
       <c r="G231" s="9"/>
       <c r="H231" s="6"/>
     </row>
-    <row r="232" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="232" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B232" s="7"/>
       <c r="D232" s="8"/>
       <c r="G232" s="9"/>
       <c r="H232" s="6"/>
     </row>
-    <row r="233" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="233" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B233" s="7"/>
       <c r="D233" s="8"/>
       <c r="G233" s="9"/>
       <c r="H233" s="6"/>
     </row>
-    <row r="234" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="234" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B234" s="7"/>
       <c r="D234" s="8"/>
       <c r="G234" s="9"/>
       <c r="H234" s="6"/>
     </row>
-    <row r="235" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="235" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B235" s="7"/>
       <c r="D235" s="8"/>
       <c r="G235" s="9"/>
       <c r="H235" s="6"/>
     </row>
-    <row r="236" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="236" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B236" s="7"/>
       <c r="D236" s="8"/>
       <c r="G236" s="9"/>
       <c r="H236" s="6"/>
     </row>
-    <row r="237" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="237" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B237" s="7"/>
       <c r="D237" s="8"/>
       <c r="G237" s="9"/>
       <c r="H237" s="6"/>
     </row>
-    <row r="238" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="238" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B238" s="7"/>
       <c r="D238" s="8"/>
       <c r="G238" s="9"/>
       <c r="H238" s="6"/>
     </row>
-    <row r="239" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="239" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B239" s="7"/>
       <c r="D239" s="8"/>
       <c r="G239" s="9"/>
       <c r="H239" s="6"/>
     </row>
-    <row r="240" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="240" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B240" s="7"/>
       <c r="D240" s="8"/>
       <c r="G240" s="9"/>
       <c r="H240" s="6"/>
     </row>
-    <row r="241" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="241" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B241" s="7"/>
       <c r="D241" s="8"/>
       <c r="G241" s="9"/>
       <c r="H241" s="6"/>
     </row>
-    <row r="242" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="242" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B242" s="7"/>
       <c r="D242" s="8"/>
       <c r="G242" s="9"/>
       <c r="H242" s="6"/>
     </row>
-    <row r="243" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="243" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B243" s="7"/>
       <c r="D243" s="8"/>
       <c r="G243" s="9"/>
       <c r="H243" s="6"/>
     </row>
-    <row r="244" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="244" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B244" s="7"/>
       <c r="D244" s="8"/>
       <c r="G244" s="9"/>
       <c r="H244" s="6"/>
     </row>
-    <row r="245" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="245" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B245" s="7"/>
       <c r="D245" s="8"/>
       <c r="G245" s="9"/>
       <c r="H245" s="6"/>
     </row>
-    <row r="246" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="246" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B246" s="7"/>
       <c r="D246" s="8"/>
       <c r="G246" s="9"/>
       <c r="H246" s="6"/>
     </row>
-    <row r="247" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="247" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B247" s="7"/>
       <c r="D247" s="8"/>
       <c r="G247" s="9"/>
       <c r="H247" s="6"/>
     </row>
-    <row r="248" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="248" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B248" s="7"/>
       <c r="D248" s="8"/>
       <c r="G248" s="9"/>
       <c r="H248" s="6"/>
     </row>
-    <row r="249" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="249" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B249" s="7"/>
       <c r="D249" s="8"/>
       <c r="G249" s="9"/>
       <c r="H249" s="6"/>
     </row>
-    <row r="250" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="250" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B250" s="7"/>
       <c r="D250" s="8"/>
       <c r="G250" s="9"/>
       <c r="H250" s="6"/>
     </row>
-    <row r="251" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="251" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B251" s="7"/>
       <c r="D251" s="8"/>
       <c r="G251" s="9"/>
       <c r="H251" s="6"/>
     </row>
-    <row r="252" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="252" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B252" s="7"/>
       <c r="D252" s="8"/>
       <c r="G252" s="9"/>
       <c r="H252" s="6"/>
     </row>
-    <row r="253" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="253" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B253" s="7"/>
       <c r="D253" s="8"/>
       <c r="G253" s="9"/>
       <c r="H253" s="6"/>
     </row>
-    <row r="254" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="254" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B254" s="7"/>
       <c r="D254" s="8"/>
       <c r="G254" s="9"/>
       <c r="H254" s="6"/>
     </row>
-    <row r="255" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="255" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B255" s="7"/>
       <c r="D255" s="8"/>
       <c r="G255" s="9"/>
       <c r="H255" s="6"/>
     </row>
-    <row r="256" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="256" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B256" s="7"/>
       <c r="D256" s="8"/>
       <c r="G256" s="9"/>
       <c r="H256" s="6"/>
     </row>
-    <row r="257" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="257" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B257" s="7"/>
       <c r="D257" s="8"/>
       <c r="G257" s="9"/>
       <c r="H257" s="6"/>
     </row>
-    <row r="258" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="258" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B258" s="7"/>
       <c r="D258" s="8"/>
       <c r="G258" s="9"/>
       <c r="H258" s="6"/>
     </row>
-    <row r="259" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="259" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B259" s="7"/>
       <c r="D259" s="8"/>
       <c r="G259" s="9"/>
       <c r="H259" s="6"/>
     </row>
-    <row r="260" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="260" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B260" s="7"/>
       <c r="D260" s="8"/>
       <c r="G260" s="9"/>
       <c r="H260" s="6"/>
     </row>
-    <row r="261" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="261" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B261" s="7"/>
       <c r="D261" s="8"/>
       <c r="G261" s="9"/>
       <c r="H261" s="6"/>
     </row>
-    <row r="262" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="262" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B262" s="7"/>
       <c r="D262" s="8"/>
       <c r="G262" s="9"/>
       <c r="H262" s="6"/>
     </row>
-    <row r="263" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="263" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B263" s="7"/>
       <c r="D263" s="8"/>
       <c r="G263" s="9"/>
       <c r="H263" s="6"/>
     </row>
-    <row r="264" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="264" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B264" s="7"/>
       <c r="D264" s="8"/>
       <c r="G264" s="9"/>
       <c r="H264" s="6"/>
     </row>
-    <row r="265" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="265" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B265" s="7"/>
       <c r="D265" s="8"/>
       <c r="G265" s="9"/>
       <c r="H265" s="6"/>
     </row>
-    <row r="266" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="266" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B266" s="7"/>
       <c r="D266" s="8"/>
       <c r="G266" s="9"/>
       <c r="H266" s="6"/>
     </row>
-    <row r="267" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="267" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B267" s="7"/>
       <c r="D267" s="8"/>
       <c r="G267" s="9"/>
       <c r="H267" s="6"/>
     </row>
-    <row r="268" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="268" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B268" s="7"/>
       <c r="D268" s="8"/>
       <c r="G268" s="9"/>
       <c r="H268" s="6"/>
     </row>
-    <row r="269" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="269" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B269" s="7"/>
       <c r="D269" s="8"/>
       <c r="G269" s="9"/>
       <c r="H269" s="6"/>
     </row>
-    <row r="270" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="270" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B270" s="7"/>
       <c r="D270" s="8"/>
       <c r="G270" s="9"/>
       <c r="H270" s="6"/>
     </row>
-    <row r="271" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="271" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B271" s="7"/>
       <c r="D271" s="8"/>
       <c r="G271" s="9"/>
       <c r="H271" s="6"/>
     </row>
-    <row r="272" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="272" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B272" s="7"/>
       <c r="D272" s="8"/>
       <c r="G272" s="9"/>
       <c r="H272" s="6"/>
     </row>
-    <row r="273" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="273" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B273" s="7"/>
       <c r="D273" s="8"/>
       <c r="G273" s="9"/>
       <c r="H273" s="6"/>
     </row>
-    <row r="274" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="274" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B274" s="7"/>
       <c r="D274" s="8"/>
       <c r="G274" s="9"/>
       <c r="H274" s="6"/>
     </row>
-    <row r="275" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="275" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B275" s="7"/>
       <c r="D275" s="8"/>
       <c r="G275" s="9"/>
       <c r="H275" s="6"/>
     </row>
-    <row r="276" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="276" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B276" s="7"/>
       <c r="D276" s="8"/>
       <c r="G276" s="9"/>
       <c r="H276" s="6"/>
     </row>
-    <row r="277" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="277" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B277" s="7"/>
       <c r="D277" s="8"/>
       <c r="G277" s="9"/>
       <c r="H277" s="6"/>
     </row>
-    <row r="278" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="278" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B278" s="7"/>
       <c r="D278" s="8"/>
       <c r="G278" s="9"/>
       <c r="H278" s="6"/>
     </row>
-    <row r="279" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="279" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B279" s="7"/>
       <c r="D279" s="8"/>
       <c r="G279" s="9"/>
       <c r="H279" s="6"/>
     </row>
-    <row r="280" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="280" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B280" s="7"/>
       <c r="D280" s="8"/>
       <c r="G280" s="9"/>
       <c r="H280" s="6"/>
     </row>
-    <row r="281" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="281" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B281" s="7"/>
       <c r="D281" s="8"/>
       <c r="G281" s="9"/>
       <c r="H281" s="6"/>
     </row>
-    <row r="282" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="282" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B282" s="7"/>
       <c r="D282" s="8"/>
       <c r="G282" s="9"/>
       <c r="H282" s="6"/>
     </row>
-    <row r="283" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="283" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B283" s="7"/>
       <c r="D283" s="8"/>
       <c r="G283" s="9"/>
       <c r="H283" s="6"/>
     </row>
-    <row r="284" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="284" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B284" s="7"/>
       <c r="D284" s="8"/>
       <c r="G284" s="9"/>
       <c r="H284" s="6"/>
     </row>
-    <row r="285" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="285" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B285" s="7"/>
       <c r="D285" s="8"/>
       <c r="G285" s="9"/>
       <c r="H285" s="6"/>
     </row>
-    <row r="286" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="286" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B286" s="7"/>
       <c r="D286" s="8"/>
       <c r="G286" s="9"/>
       <c r="H286" s="6"/>
     </row>
-    <row r="287" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="287" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B287" s="7"/>
       <c r="D287" s="8"/>
       <c r="G287" s="9"/>
       <c r="H287" s="6"/>
     </row>
-    <row r="288" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="288" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B288" s="7"/>
       <c r="D288" s="8"/>
       <c r="G288" s="9"/>
       <c r="H288" s="6"/>
     </row>
-    <row r="289" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="289" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B289" s="7"/>
       <c r="D289" s="8"/>
       <c r="G289" s="9"/>
       <c r="H289" s="6"/>
     </row>
-    <row r="290" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="290" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B290" s="7"/>
       <c r="D290" s="8"/>
       <c r="G290" s="9"/>
       <c r="H290" s="6"/>
     </row>
-    <row r="291" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="291" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B291" s="7"/>
       <c r="D291" s="8"/>
       <c r="G291" s="9"/>
       <c r="H291" s="6"/>
     </row>
-    <row r="292" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="292" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B292" s="7"/>
       <c r="D292" s="8"/>
       <c r="G292" s="9"/>
       <c r="H292" s="6"/>
     </row>
-    <row r="293" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="293" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B293" s="7"/>
       <c r="D293" s="8"/>
       <c r="G293" s="9"/>
       <c r="H293" s="6"/>
     </row>
-    <row r="294" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="294" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B294" s="7"/>
       <c r="D294" s="8"/>
       <c r="G294" s="9"/>
       <c r="H294" s="6"/>
     </row>
-    <row r="295" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="295" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B295" s="7"/>
       <c r="D295" s="8"/>
       <c r="G295" s="9"/>
       <c r="H295" s="6"/>
     </row>
-    <row r="296" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="296" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B296" s="7"/>
       <c r="D296" s="8"/>
       <c r="G296" s="9"/>
       <c r="H296" s="6"/>
     </row>
-    <row r="297" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="297" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B297" s="7"/>
       <c r="D297" s="8"/>
       <c r="G297" s="9"/>
       <c r="H297" s="6"/>
     </row>
-    <row r="298" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="298" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B298" s="7"/>
       <c r="D298" s="8"/>
       <c r="G298" s="9"/>
       <c r="H298" s="6"/>
     </row>
-    <row r="299" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="299" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B299" s="7"/>
       <c r="D299" s="8"/>
       <c r="G299" s="9"/>
       <c r="H299" s="6"/>
     </row>
-    <row r="300" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="300" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B300" s="7"/>
       <c r="D300" s="8"/>
       <c r="G300" s="9"/>
       <c r="H300" s="6"/>
     </row>
-    <row r="301" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="301" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B301" s="7"/>
       <c r="D301" s="8"/>
       <c r="G301" s="9"/>
       <c r="H301" s="6"/>
     </row>
-    <row r="302" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="302" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B302" s="7"/>
       <c r="D302" s="8"/>
       <c r="G302" s="9"/>
       <c r="H302" s="6"/>
     </row>
-    <row r="303" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="303" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B303" s="7"/>
       <c r="D303" s="8"/>
       <c r="G303" s="9"/>
       <c r="H303" s="6"/>
     </row>
-    <row r="304" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="304" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B304" s="7"/>
       <c r="D304" s="8"/>
       <c r="G304" s="9"/>
       <c r="H304" s="6"/>
     </row>
-    <row r="305" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="305" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B305" s="7"/>
       <c r="D305" s="8"/>
       <c r="G305" s="9"/>
       <c r="H305" s="6"/>
     </row>
-    <row r="306" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="306" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B306" s="7"/>
       <c r="D306" s="8"/>
       <c r="G306" s="9"/>
       <c r="H306" s="6"/>
     </row>
-    <row r="307" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="307" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B307" s="7"/>
       <c r="D307" s="8"/>
       <c r="G307" s="9"/>
       <c r="H307" s="6"/>
     </row>
-    <row r="308" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="308" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B308" s="7"/>
       <c r="D308" s="8"/>
       <c r="G308" s="9"/>
       <c r="H308" s="6"/>
     </row>
-    <row r="309" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="309" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B309" s="7"/>
       <c r="D309" s="8"/>
       <c r="G309" s="9"/>
       <c r="H309" s="6"/>
     </row>
-    <row r="310" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="310" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B310" s="7"/>
       <c r="D310" s="8"/>
       <c r="G310" s="9"/>
       <c r="H310" s="6"/>
     </row>
-    <row r="311" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="311" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B311" s="7"/>
       <c r="D311" s="8"/>
       <c r="G311" s="9"/>
       <c r="H311" s="6"/>
     </row>
-    <row r="312" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="312" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B312" s="7"/>
       <c r="D312" s="8"/>
       <c r="G312" s="9"/>
       <c r="H312" s="6"/>
     </row>
-    <row r="313" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="313" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B313" s="7"/>
       <c r="D313" s="8"/>
       <c r="G313" s="9"/>
       <c r="H313" s="6"/>
     </row>
-    <row r="314" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="314" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B314" s="7"/>
       <c r="D314" s="8"/>
       <c r="G314" s="9"/>
       <c r="H314" s="6"/>
     </row>
-    <row r="315" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="315" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B315" s="7"/>
       <c r="D315" s="8"/>
       <c r="G315" s="9"/>
       <c r="H315" s="6"/>
     </row>
-    <row r="316" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="316" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B316" s="7"/>
       <c r="D316" s="8"/>
       <c r="G316" s="9"/>
       <c r="H316" s="6"/>
     </row>
-    <row r="317" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="317" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B317" s="7"/>
       <c r="D317" s="8"/>
       <c r="G317" s="9"/>
       <c r="H317" s="6"/>
     </row>
-    <row r="318" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="318" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B318" s="7"/>
       <c r="D318" s="8"/>
       <c r="G318" s="9"/>
       <c r="H318" s="6"/>
     </row>
-    <row r="319" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="319" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B319" s="7"/>
       <c r="D319" s="8"/>
       <c r="G319" s="9"/>
       <c r="H319" s="6"/>
     </row>
-    <row r="320" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="320" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B320" s="7"/>
       <c r="D320" s="8"/>
       <c r="G320" s="9"/>
       <c r="H320" s="6"/>
     </row>
-    <row r="321" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="321" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B321" s="7"/>
       <c r="D321" s="8"/>
       <c r="G321" s="9"/>
       <c r="H321" s="6"/>
     </row>
-    <row r="322" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="322" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B322" s="7"/>
       <c r="D322" s="8"/>
       <c r="G322" s="9"/>
       <c r="H322" s="6"/>
     </row>
-    <row r="323" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="323" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B323" s="7"/>
       <c r="D323" s="8"/>
       <c r="G323" s="9"/>
       <c r="H323" s="6"/>
     </row>
-    <row r="324" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="324" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B324" s="7"/>
       <c r="D324" s="8"/>
       <c r="G324" s="9"/>
       <c r="H324" s="6"/>
     </row>
-    <row r="325" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="325" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B325" s="7"/>
       <c r="D325" s="8"/>
       <c r="G325" s="9"/>
       <c r="H325" s="6"/>
     </row>
-    <row r="326" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="326" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B326" s="7"/>
       <c r="D326" s="8"/>
       <c r="G326" s="9"/>
       <c r="H326" s="6"/>
     </row>
-    <row r="327" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="327" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B327" s="7"/>
       <c r="D327" s="8"/>
       <c r="G327" s="9"/>
       <c r="H327" s="6"/>
     </row>
-    <row r="328" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="328" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B328" s="7"/>
       <c r="D328" s="8"/>
       <c r="G328" s="9"/>
       <c r="H328" s="6"/>
     </row>
-    <row r="329" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="329" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B329" s="7"/>
       <c r="D329" s="8"/>
       <c r="G329" s="9"/>
       <c r="H329" s="6"/>
     </row>
-    <row r="330" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="330" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B330" s="7"/>
       <c r="D330" s="8"/>
       <c r="G330" s="9"/>
       <c r="H330" s="6"/>
     </row>
-    <row r="331" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="331" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B331" s="7"/>
       <c r="D331" s="8"/>
       <c r="G331" s="9"/>
       <c r="H331" s="6"/>
     </row>
-    <row r="332" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="332" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B332" s="7"/>
       <c r="D332" s="8"/>
       <c r="G332" s="9"/>
       <c r="H332" s="6"/>
     </row>
-    <row r="333" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="333" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B333" s="7"/>
       <c r="D333" s="8"/>
       <c r="G333" s="9"/>
       <c r="H333" s="6"/>
     </row>
-    <row r="334" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="334" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B334" s="7"/>
       <c r="D334" s="8"/>
       <c r="G334" s="9"/>
       <c r="H334" s="6"/>
     </row>
-    <row r="335" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="335" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B335" s="7"/>
       <c r="D335" s="8"/>
       <c r="G335" s="9"/>
       <c r="H335" s="6"/>
     </row>
-    <row r="336" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="336" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B336" s="7"/>
       <c r="D336" s="8"/>
       <c r="G336" s="9"/>
       <c r="H336" s="6"/>
     </row>
-    <row r="337" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="337" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B337" s="7"/>
       <c r="D337" s="8"/>
       <c r="G337" s="9"/>
       <c r="H337" s="6"/>
     </row>
-    <row r="338" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="338" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B338" s="7"/>
       <c r="D338" s="8"/>
       <c r="G338" s="9"/>
       <c r="H338" s="6"/>
     </row>
-    <row r="339" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="339" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B339" s="7"/>
       <c r="D339" s="8"/>
       <c r="G339" s="9"/>
       <c r="H339" s="6"/>
     </row>
-    <row r="340" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="340" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B340" s="7"/>
       <c r="D340" s="8"/>
       <c r="G340" s="9"/>
       <c r="H340" s="6"/>
     </row>
-    <row r="341" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="341" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B341" s="7"/>
       <c r="D341" s="8"/>
       <c r="G341" s="9"/>
       <c r="H341" s="6"/>
     </row>
-    <row r="342" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="342" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B342" s="7"/>
       <c r="D342" s="8"/>
       <c r="G342" s="9"/>
       <c r="H342" s="6"/>
     </row>
-    <row r="343" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="343" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B343" s="7"/>
       <c r="D343" s="8"/>
       <c r="G343" s="9"/>
       <c r="H343" s="6"/>
     </row>
-    <row r="344" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="344" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B344" s="7"/>
       <c r="D344" s="8"/>
       <c r="G344" s="9"/>
       <c r="H344" s="6"/>
     </row>
-    <row r="345" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="345" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B345" s="7"/>
       <c r="D345" s="8"/>
       <c r="G345" s="9"/>
       <c r="H345" s="6"/>
     </row>
-    <row r="346" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="346" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B346" s="7"/>
       <c r="D346" s="8"/>
       <c r="G346" s="9"/>
       <c r="H346" s="6"/>
     </row>
-    <row r="347" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="347" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B347" s="7"/>
       <c r="D347" s="8"/>
       <c r="G347" s="9"/>
       <c r="H347" s="6"/>
     </row>
-    <row r="348" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="348" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B348" s="7"/>
       <c r="D348" s="8"/>
       <c r="G348" s="9"/>
       <c r="H348" s="6"/>
     </row>
-    <row r="349" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="349" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B349" s="7"/>
       <c r="D349" s="8"/>
       <c r="G349" s="9"/>
       <c r="H349" s="6"/>
     </row>
-    <row r="350" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="350" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B350" s="7"/>
       <c r="D350" s="8"/>
       <c r="G350" s="9"/>
       <c r="H350" s="6"/>
     </row>
-    <row r="351" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="351" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B351" s="7"/>
       <c r="D351" s="8"/>
       <c r="G351" s="9"/>
       <c r="H351" s="6"/>
     </row>
-    <row r="352" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="352" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B352" s="7"/>
       <c r="D352" s="8"/>
       <c r="G352" s="9"/>
       <c r="H352" s="6"/>
     </row>
-    <row r="353" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="353" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B353" s="7"/>
       <c r="D353" s="8"/>
       <c r="G353" s="9"/>
       <c r="H353" s="6"/>
     </row>
-    <row r="354" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="354" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B354" s="7"/>
       <c r="D354" s="8"/>
       <c r="G354" s="9"/>
       <c r="H354" s="6"/>
     </row>
-    <row r="355" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="355" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B355" s="7"/>
       <c r="D355" s="8"/>
       <c r="G355" s="9"/>
       <c r="H355" s="6"/>
     </row>
-    <row r="356" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="356" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B356" s="7"/>
       <c r="D356" s="8"/>
       <c r="G356" s="9"/>
       <c r="H356" s="6"/>
     </row>
-    <row r="357" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="357" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B357" s="7"/>
       <c r="D357" s="8"/>
       <c r="G357" s="9"/>
       <c r="H357" s="6"/>
     </row>
-    <row r="358" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="358" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B358" s="7"/>
       <c r="D358" s="8"/>
       <c r="G358" s="9"/>
       <c r="H358" s="6"/>
     </row>
-    <row r="359" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="359" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B359" s="7"/>
       <c r="D359" s="8"/>
       <c r="G359" s="9"/>
       <c r="H359" s="6"/>
     </row>
-    <row r="360" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="360" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B360" s="7"/>
       <c r="D360" s="8"/>
       <c r="G360" s="9"/>
       <c r="H360" s="6"/>
     </row>
-    <row r="361" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="361" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B361" s="7"/>
       <c r="D361" s="8"/>
       <c r="G361" s="9"/>
       <c r="H361" s="6"/>
     </row>
-    <row r="362" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="362" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B362" s="7"/>
       <c r="D362" s="8"/>
       <c r="G362" s="9"/>
       <c r="H362" s="6"/>
     </row>
-    <row r="363" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="363" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B363" s="7"/>
       <c r="D363" s="8"/>
       <c r="G363" s="9"/>
       <c r="H363" s="6"/>
     </row>
-    <row r="364" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="364" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B364" s="7"/>
       <c r="D364" s="8"/>
       <c r="G364" s="9"/>
       <c r="H364" s="6"/>
     </row>
-    <row r="365" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="365" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B365" s="7"/>
       <c r="D365" s="8"/>
       <c r="G365" s="9"/>
       <c r="H365" s="6"/>
     </row>
-    <row r="366" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="366" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B366" s="7"/>
       <c r="D366" s="8"/>
       <c r="G366" s="9"/>
       <c r="H366" s="6"/>
     </row>
-    <row r="367" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="367" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B367" s="7"/>
       <c r="D367" s="8"/>
       <c r="G367" s="9"/>
       <c r="H367" s="6"/>
     </row>
-    <row r="368" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="368" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B368" s="7"/>
       <c r="D368" s="8"/>
       <c r="G368" s="9"/>
       <c r="H368" s="6"/>
     </row>
-    <row r="369" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="369" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B369" s="7"/>
       <c r="D369" s="8"/>
       <c r="G369" s="9"/>
       <c r="H369" s="6"/>
     </row>
-    <row r="370" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="370" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B370" s="7"/>
       <c r="D370" s="8"/>
       <c r="G370" s="9"/>
       <c r="H370" s="6"/>
     </row>
-    <row r="371" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="371" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B371" s="7"/>
       <c r="D371" s="8"/>
       <c r="G371" s="9"/>
       <c r="H371" s="6"/>
     </row>
-    <row r="372" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="372" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B372" s="7"/>
       <c r="D372" s="8"/>
       <c r="G372" s="9"/>
       <c r="H372" s="6"/>
     </row>
-    <row r="373" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="373" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B373" s="7"/>
       <c r="D373" s="8"/>
       <c r="G373" s="9"/>
       <c r="H373" s="6"/>
     </row>
-    <row r="374" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="374" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B374" s="7"/>
       <c r="D374" s="8"/>
       <c r="G374" s="9"/>
       <c r="H374" s="6"/>
     </row>
-    <row r="375" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="375" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B375" s="7"/>
       <c r="D375" s="8"/>
       <c r="G375" s="9"/>
       <c r="H375" s="6"/>
     </row>
-    <row r="376" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="376" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B376" s="7"/>
       <c r="D376" s="8"/>
       <c r="G376" s="9"/>
       <c r="H376" s="6"/>
     </row>
-    <row r="377" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="377" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B377" s="7"/>
       <c r="D377" s="8"/>
       <c r="G377" s="9"/>
       <c r="H377" s="6"/>
     </row>
-    <row r="378" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="378" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B378" s="7"/>
       <c r="D378" s="8"/>
       <c r="G378" s="9"/>
       <c r="H378" s="6"/>
     </row>
-    <row r="379" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="379" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B379" s="7"/>
       <c r="D379" s="8"/>
       <c r="G379" s="9"/>
       <c r="H379" s="6"/>
     </row>
-    <row r="380" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="380" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B380" s="7"/>
       <c r="D380" s="8"/>
       <c r="G380" s="9"/>
       <c r="H380" s="6"/>
     </row>
-    <row r="381" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="381" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B381" s="7"/>
       <c r="D381" s="8"/>
       <c r="G381" s="9"/>
       <c r="H381" s="6"/>
     </row>
-    <row r="382" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="382" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B382" s="7"/>
       <c r="D382" s="8"/>
       <c r="G382" s="9"/>
       <c r="H382" s="6"/>
     </row>
-    <row r="383" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="383" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B383" s="7"/>
       <c r="D383" s="8"/>
       <c r="G383" s="9"/>
       <c r="H383" s="6"/>
     </row>
-    <row r="384" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="384" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B384" s="7"/>
       <c r="D384" s="8"/>
       <c r="G384" s="9"/>
       <c r="H384" s="6"/>
     </row>
-    <row r="385" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="385" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B385" s="7"/>
       <c r="D385" s="8"/>
       <c r="G385" s="9"/>
       <c r="H385" s="6"/>
     </row>
-    <row r="386" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="386" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B386" s="7"/>
       <c r="D386" s="8"/>
       <c r="G386" s="9"/>
       <c r="H386" s="6"/>
     </row>
-    <row r="387" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="387" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B387" s="7"/>
       <c r="D387" s="8"/>
       <c r="G387" s="9"/>
       <c r="H387" s="6"/>
     </row>
-    <row r="388" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="388" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B388" s="7"/>
       <c r="D388" s="8"/>
       <c r="G388" s="9"/>
       <c r="H388" s="6"/>
     </row>
-    <row r="389" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="389" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B389" s="7"/>
       <c r="D389" s="8"/>
       <c r="G389" s="9"/>
       <c r="H389" s="6"/>
     </row>
-    <row r="390" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="390" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B390" s="7"/>
       <c r="D390" s="8"/>
       <c r="G390" s="9"/>
       <c r="H390" s="6"/>
     </row>
-    <row r="391" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="391" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B391" s="7"/>
       <c r="D391" s="8"/>
       <c r="G391" s="9"/>
       <c r="H391" s="6"/>
     </row>
-    <row r="392" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="392" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B392" s="7"/>
       <c r="D392" s="8"/>
       <c r="G392" s="9"/>
       <c r="H392" s="6"/>
     </row>
-    <row r="393" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="393" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B393" s="7"/>
       <c r="D393" s="8"/>
       <c r="G393" s="9"/>
       <c r="H393" s="6"/>
     </row>
-    <row r="394" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="394" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B394" s="7"/>
       <c r="D394" s="8"/>
       <c r="G394" s="9"/>
       <c r="H394" s="6"/>
     </row>
-    <row r="395" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="395" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B395" s="7"/>
       <c r="D395" s="8"/>
       <c r="G395" s="9"/>
       <c r="H395" s="6"/>
     </row>
-    <row r="396" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="396" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B396" s="7"/>
       <c r="D396" s="8"/>
       <c r="G396" s="9"/>
       <c r="H396" s="6"/>
     </row>
-    <row r="397" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="397" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B397" s="7"/>
       <c r="D397" s="8"/>
       <c r="G397" s="9"/>
       <c r="H397" s="6"/>
     </row>
-    <row r="398" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="398" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B398" s="7"/>
       <c r="D398" s="8"/>
       <c r="G398" s="9"/>
       <c r="H398" s="6"/>
     </row>
-    <row r="399" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="399" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B399" s="7"/>
       <c r="D399" s="8"/>
       <c r="G399" s="9"/>
       <c r="H399" s="6"/>
     </row>
-    <row r="400" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="400" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B400" s="7"/>
       <c r="D400" s="8"/>
       <c r="G400" s="9"/>
       <c r="H400" s="6"/>
     </row>
-    <row r="401" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="401" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B401" s="7"/>
       <c r="D401" s="8"/>
       <c r="G401" s="9"/>
       <c r="H401" s="6"/>
     </row>
-    <row r="402" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="402" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B402" s="7"/>
       <c r="D402" s="8"/>
       <c r="G402" s="9"/>
       <c r="H402" s="6"/>
     </row>
-    <row r="403" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="403" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B403" s="7"/>
       <c r="D403" s="8"/>
       <c r="G403" s="9"/>
       <c r="H403" s="6"/>
     </row>
-    <row r="404" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="404" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B404" s="7"/>
       <c r="D404" s="8"/>
       <c r="G404" s="9"/>
       <c r="H404" s="6"/>
     </row>
-    <row r="405" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="405" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B405" s="7"/>
       <c r="D405" s="8"/>
       <c r="G405" s="9"/>
       <c r="H405" s="6"/>
     </row>
-    <row r="406" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="406" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B406" s="7"/>
       <c r="D406" s="8"/>
       <c r="G406" s="9"/>
       <c r="H406" s="6"/>
     </row>
-    <row r="407" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="407" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B407" s="7"/>
       <c r="D407" s="8"/>
       <c r="G407" s="9"/>
       <c r="H407" s="6"/>
     </row>
-    <row r="408" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="408" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B408" s="7"/>
       <c r="D408" s="8"/>
       <c r="G408" s="9"/>
       <c r="H408" s="6"/>
     </row>
-    <row r="409" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="409" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B409" s="7"/>
       <c r="D409" s="8"/>
       <c r="G409" s="9"/>
       <c r="H409" s="6"/>
     </row>
-    <row r="410" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="410" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B410" s="7"/>
       <c r="D410" s="8"/>
       <c r="G410" s="9"/>
       <c r="H410" s="6"/>
     </row>
-    <row r="411" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="411" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B411" s="7"/>
       <c r="D411" s="8"/>
       <c r="G411" s="9"/>
       <c r="H411" s="6"/>
     </row>
-    <row r="412" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="412" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B412" s="7"/>
       <c r="D412" s="8"/>
       <c r="G412" s="9"/>
       <c r="H412" s="6"/>
     </row>
-    <row r="413" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="413" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B413" s="7"/>
       <c r="D413" s="8"/>
       <c r="G413" s="9"/>
       <c r="H413" s="6"/>
     </row>
-    <row r="414" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="414" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B414" s="7"/>
       <c r="D414" s="8"/>
       <c r="G414" s="9"/>
       <c r="H414" s="6"/>
     </row>
-    <row r="415" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="415" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B415" s="7"/>
       <c r="D415" s="8"/>
       <c r="G415" s="9"/>
       <c r="H415" s="6"/>
     </row>
-    <row r="416" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="416" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B416" s="7"/>
       <c r="D416" s="8"/>
       <c r="G416" s="9"/>
       <c r="H416" s="6"/>
     </row>
-    <row r="417" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="417" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B417" s="7"/>
       <c r="D417" s="8"/>
       <c r="G417" s="9"/>
       <c r="H417" s="6"/>
     </row>
-    <row r="418" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="418" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B418" s="7"/>
       <c r="D418" s="8"/>
       <c r="G418" s="9"/>
       <c r="H418" s="6"/>
     </row>
-    <row r="419" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="419" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B419" s="7"/>
       <c r="D419" s="8"/>
       <c r="G419" s="9"/>
       <c r="H419" s="6"/>
     </row>
-    <row r="420" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="420" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B420" s="7"/>
       <c r="D420" s="8"/>
       <c r="G420" s="9"/>
       <c r="H420" s="6"/>
     </row>
-    <row r="421" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="421" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B421" s="7"/>
       <c r="D421" s="8"/>
       <c r="G421" s="9"/>
       <c r="H421" s="6"/>
     </row>
-    <row r="422" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="422" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B422" s="7"/>
       <c r="D422" s="8"/>
       <c r="G422" s="9"/>
       <c r="H422" s="6"/>
     </row>
-    <row r="423" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="423" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B423" s="7"/>
       <c r="D423" s="8"/>
       <c r="G423" s="9"/>
       <c r="H423" s="6"/>
     </row>
-    <row r="424" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="424" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B424" s="7"/>
       <c r="D424" s="8"/>
       <c r="G424" s="9"/>
       <c r="H424" s="6"/>
     </row>
-    <row r="425" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="425" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B425" s="7"/>
       <c r="D425" s="8"/>
       <c r="G425" s="9"/>
       <c r="H425" s="6"/>
     </row>
-    <row r="426" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="426" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B426" s="7"/>
       <c r="D426" s="8"/>
       <c r="G426" s="9"/>
       <c r="H426" s="6"/>
     </row>
-    <row r="427" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="427" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B427" s="7"/>
       <c r="D427" s="8"/>
       <c r="G427" s="9"/>
       <c r="H427" s="6"/>
     </row>
-    <row r="428" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="428" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B428" s="7"/>
       <c r="D428" s="8"/>
       <c r="G428" s="9"/>
       <c r="H428" s="6"/>
     </row>
-    <row r="429" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="429" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B429" s="7"/>
       <c r="D429" s="8"/>
       <c r="G429" s="9"/>
       <c r="H429" s="6"/>
     </row>
-    <row r="430" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="430" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B430" s="7"/>
       <c r="D430" s="8"/>
       <c r="G430" s="9"/>
       <c r="H430" s="6"/>
     </row>
-    <row r="431" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="431" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B431" s="7"/>
       <c r="D431" s="8"/>
       <c r="G431" s="9"/>
       <c r="H431" s="6"/>
     </row>
-    <row r="432" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="432" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B432" s="7"/>
       <c r="D432" s="8"/>
       <c r="G432" s="9"/>
       <c r="H432" s="6"/>
     </row>
-    <row r="433" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="433" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B433" s="7"/>
       <c r="D433" s="8"/>
       <c r="G433" s="9"/>
       <c r="H433" s="6"/>
     </row>
-    <row r="434" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="434" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B434" s="7"/>
       <c r="D434" s="8"/>
       <c r="G434" s="9"/>
       <c r="H434" s="6"/>
     </row>
-    <row r="435" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="435" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B435" s="7"/>
       <c r="D435" s="8"/>
       <c r="G435" s="9"/>
       <c r="H435" s="6"/>
     </row>
-    <row r="436" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="436" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B436" s="7"/>
       <c r="D436" s="8"/>
       <c r="G436" s="9"/>
       <c r="H436" s="6"/>
     </row>
-    <row r="437" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="437" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B437" s="7"/>
       <c r="D437" s="8"/>
       <c r="G437" s="9"/>
       <c r="H437" s="6"/>
     </row>
-    <row r="438" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="438" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B438" s="7"/>
       <c r="D438" s="8"/>
       <c r="G438" s="9"/>
       <c r="H438" s="6"/>
     </row>
-    <row r="439" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="439" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B439" s="7"/>
       <c r="D439" s="8"/>
       <c r="G439" s="9"/>
       <c r="H439" s="6"/>
     </row>
-    <row r="440" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="440" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B440" s="7"/>
       <c r="D440" s="8"/>
       <c r="G440" s="9"/>
       <c r="H440" s="6"/>
     </row>
-    <row r="441" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="441" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B441" s="7"/>
       <c r="D441" s="8"/>
       <c r="G441" s="9"/>
       <c r="H441" s="6"/>
     </row>
-    <row r="442" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="442" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B442" s="7"/>
       <c r="D442" s="8"/>
       <c r="G442" s="9"/>
       <c r="H442" s="6"/>
     </row>
-    <row r="443" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="443" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B443" s="7"/>
       <c r="D443" s="8"/>
       <c r="G443" s="9"/>
       <c r="H443" s="6"/>
     </row>
-    <row r="444" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="444" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B444" s="7"/>
       <c r="D444" s="8"/>
       <c r="G444" s="9"/>
       <c r="H444" s="6"/>
     </row>
-    <row r="445" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="445" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B445" s="7"/>
       <c r="D445" s="8"/>
       <c r="G445" s="9"/>
       <c r="H445" s="6"/>
     </row>
-    <row r="446" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="446" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B446" s="7"/>
       <c r="D446" s="8"/>
       <c r="G446" s="9"/>
       <c r="H446" s="6"/>
     </row>
-    <row r="447" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="447" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B447" s="7"/>
       <c r="D447" s="8"/>
       <c r="G447" s="9"/>
       <c r="H447" s="6"/>
     </row>
-    <row r="448" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="448" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B448" s="7"/>
       <c r="D448" s="8"/>
       <c r="G448" s="9"/>
       <c r="H448" s="6"/>
     </row>
-    <row r="449" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="449" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B449" s="7"/>
       <c r="D449" s="8"/>
       <c r="G449" s="9"/>
       <c r="H449" s="6"/>
     </row>
-    <row r="450" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="450" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B450" s="7"/>
       <c r="D450" s="8"/>
       <c r="G450" s="9"/>
       <c r="H450" s="6"/>
     </row>
-    <row r="451" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="451" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B451" s="7"/>
       <c r="D451" s="8"/>
       <c r="G451" s="9"/>
       <c r="H451" s="6"/>
     </row>
-    <row r="452" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="452" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B452" s="7"/>
       <c r="D452" s="8"/>
       <c r="G452" s="9"/>
       <c r="H452" s="6"/>
     </row>
-    <row r="453" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="453" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B453" s="7"/>
       <c r="D453" s="8"/>
       <c r="G453" s="9"/>
       <c r="H453" s="6"/>
     </row>
-    <row r="454" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="454" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B454" s="7"/>
       <c r="D454" s="8"/>
       <c r="G454" s="9"/>
       <c r="H454" s="6"/>
     </row>
-    <row r="455" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="455" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B455" s="7"/>
       <c r="D455" s="8"/>
       <c r="G455" s="9"/>
       <c r="H455" s="6"/>
     </row>
-    <row r="456" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="456" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B456" s="7"/>
       <c r="D456" s="8"/>
       <c r="G456" s="9"/>
       <c r="H456" s="6"/>
     </row>
-    <row r="457" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="457" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B457" s="7"/>
       <c r="D457" s="8"/>
       <c r="G457" s="9"/>
       <c r="H457" s="6"/>
     </row>
-    <row r="458" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="458" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B458" s="7"/>
       <c r="D458" s="8"/>
       <c r="G458" s="9"/>
       <c r="H458" s="6"/>
     </row>
-    <row r="459" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="459" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B459" s="7"/>
       <c r="D459" s="8"/>
       <c r="G459" s="9"/>
       <c r="H459" s="6"/>
     </row>
-    <row r="460" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="460" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B460" s="7"/>
       <c r="D460" s="8"/>
       <c r="G460" s="9"/>
       <c r="H460" s="6"/>
     </row>
-    <row r="461" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="461" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B461" s="7"/>
       <c r="D461" s="8"/>
       <c r="G461" s="9"/>
       <c r="H461" s="6"/>
     </row>
-    <row r="462" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="462" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B462" s="7"/>
       <c r="D462" s="8"/>
       <c r="G462" s="9"/>
       <c r="H462" s="6"/>
     </row>
-    <row r="463" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="463" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B463" s="7"/>
       <c r="D463" s="8"/>
       <c r="G463" s="9"/>
       <c r="H463" s="6"/>
     </row>
-    <row r="464" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="464" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B464" s="7"/>
       <c r="D464" s="8"/>
       <c r="G464" s="9"/>
       <c r="H464" s="6"/>
     </row>
-    <row r="465" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="465" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B465" s="7"/>
       <c r="D465" s="8"/>
       <c r="G465" s="9"/>
       <c r="H465" s="6"/>
     </row>
-    <row r="466" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="466" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B466" s="7"/>
       <c r="D466" s="8"/>
       <c r="G466" s="9"/>
       <c r="H466" s="6"/>
     </row>
-    <row r="467" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="467" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B467" s="7"/>
       <c r="D467" s="8"/>
       <c r="G467" s="9"/>
       <c r="H467" s="6"/>
     </row>
-    <row r="468" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="468" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B468" s="7"/>
       <c r="D468" s="8"/>
       <c r="G468" s="9"/>
       <c r="H468" s="6"/>
     </row>
-    <row r="469" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="469" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B469" s="7"/>
       <c r="D469" s="8"/>
       <c r="G469" s="9"/>
       <c r="H469" s="6"/>
     </row>
-    <row r="470" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="470" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B470" s="7"/>
       <c r="D470" s="8"/>
       <c r="G470" s="9"/>
       <c r="H470" s="6"/>
     </row>
-    <row r="471" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="471" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B471" s="7"/>
       <c r="D471" s="8"/>
       <c r="G471" s="9"/>
       <c r="H471" s="6"/>
     </row>
-    <row r="472" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="472" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B472" s="7"/>
       <c r="D472" s="8"/>
       <c r="G472" s="9"/>
       <c r="H472" s="6"/>
     </row>
-    <row r="473" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="473" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B473" s="7"/>
       <c r="D473" s="8"/>
       <c r="G473" s="9"/>
       <c r="H473" s="6"/>
     </row>
-    <row r="474" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="474" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B474" s="7"/>
       <c r="D474" s="8"/>
       <c r="G474" s="9"/>
       <c r="H474" s="6"/>
     </row>
-    <row r="475" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="475" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B475" s="7"/>
       <c r="D475" s="8"/>
       <c r="G475" s="9"/>
       <c r="H475" s="6"/>
     </row>
-    <row r="476" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="476" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B476" s="7"/>
       <c r="D476" s="8"/>
       <c r="G476" s="9"/>
       <c r="H476" s="6"/>
     </row>
-    <row r="477" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="477" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B477" s="7"/>
       <c r="D477" s="8"/>
       <c r="G477" s="9"/>
       <c r="H477" s="6"/>
     </row>
-    <row r="478" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="478" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B478" s="7"/>
       <c r="D478" s="8"/>
       <c r="G478" s="9"/>
       <c r="H478" s="6"/>
     </row>
-    <row r="479" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="479" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B479" s="7"/>
       <c r="D479" s="8"/>
       <c r="G479" s="9"/>
       <c r="H479" s="6"/>
     </row>
-    <row r="480" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="480" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B480" s="7"/>
       <c r="D480" s="8"/>
       <c r="G480" s="9"/>
       <c r="H480" s="6"/>
     </row>
-    <row r="481" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="481" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B481" s="7"/>
       <c r="D481" s="8"/>
       <c r="G481" s="9"/>
       <c r="H481" s="6"/>
     </row>
-    <row r="482" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="482" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B482" s="7"/>
       <c r="D482" s="8"/>
       <c r="G482" s="9"/>
       <c r="H482" s="6"/>
     </row>
-    <row r="483" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="483" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B483" s="7"/>
       <c r="D483" s="8"/>
       <c r="G483" s="9"/>
       <c r="H483" s="6"/>
     </row>
-    <row r="484" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="484" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B484" s="7"/>
       <c r="D484" s="8"/>
       <c r="G484" s="9"/>
       <c r="H484" s="6"/>
     </row>
-    <row r="485" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="485" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B485" s="7"/>
       <c r="D485" s="8"/>
       <c r="G485" s="9"/>
       <c r="H485" s="6"/>
     </row>
-    <row r="486" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="486" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B486" s="7"/>
       <c r="D486" s="8"/>
       <c r="G486" s="9"/>
       <c r="H486" s="6"/>
     </row>
-    <row r="487" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="487" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B487" s="7"/>
       <c r="D487" s="8"/>
       <c r="G487" s="9"/>
       <c r="H487" s="6"/>
     </row>
-    <row r="488" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="488" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B488" s="7"/>
       <c r="D488" s="8"/>
       <c r="G488" s="9"/>
       <c r="H488" s="6"/>
     </row>
-    <row r="489" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="489" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B489" s="7"/>
       <c r="D489" s="8"/>
       <c r="G489" s="9"/>
       <c r="H489" s="6"/>
     </row>
-    <row r="490" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="490" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B490" s="7"/>
       <c r="D490" s="8"/>
       <c r="G490" s="9"/>
       <c r="H490" s="6"/>
     </row>
-    <row r="491" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="491" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B491" s="7"/>
       <c r="D491" s="8"/>
       <c r="G491" s="9"/>
       <c r="H491" s="6"/>
     </row>
-    <row r="492" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="492" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B492" s="7"/>
       <c r="D492" s="8"/>
       <c r="G492" s="9"/>
       <c r="H492" s="6"/>
     </row>
-    <row r="493" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="493" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B493" s="7"/>
       <c r="D493" s="8"/>
       <c r="G493" s="9"/>
       <c r="H493" s="6"/>
     </row>
-    <row r="494" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="494" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B494" s="7"/>
       <c r="D494" s="8"/>
       <c r="G494" s="9"/>
       <c r="H494" s="6"/>
     </row>
-    <row r="495" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="495" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B495" s="7"/>
       <c r="D495" s="8"/>
       <c r="G495" s="9"/>
       <c r="H495" s="6"/>
     </row>
-    <row r="496" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="496" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B496" s="7"/>
       <c r="D496" s="8"/>
       <c r="G496" s="9"/>
       <c r="H496" s="6"/>
     </row>
-    <row r="497" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="497" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B497" s="7"/>
       <c r="D497" s="8"/>
       <c r="G497" s="9"/>
       <c r="H497" s="6"/>
     </row>
-    <row r="498" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="498" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B498" s="7"/>
       <c r="D498" s="8"/>
       <c r="G498" s="9"/>
       <c r="H498" s="6"/>
     </row>
-    <row r="499" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="499" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B499" s="7"/>
       <c r="D499" s="8"/>
       <c r="G499" s="9"/>
       <c r="H499" s="6"/>
     </row>
-    <row r="500" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="500" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B500" s="7"/>
       <c r="D500" s="8"/>
       <c r="G500" s="9"/>
       <c r="H500" s="6"/>
     </row>
-    <row r="501" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="501" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B501" s="7"/>
       <c r="D501" s="8"/>
       <c r="G501" s="9"/>
       <c r="H501" s="6"/>
     </row>
-    <row r="502" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="502" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B502" s="7"/>
       <c r="D502" s="8"/>
       <c r="G502" s="9"/>
       <c r="H502" s="6"/>
     </row>
-    <row r="503" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="503" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B503" s="7"/>
       <c r="D503" s="8"/>
       <c r="G503" s="9"/>
       <c r="H503" s="6"/>
     </row>
-    <row r="504" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="504" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B504" s="7"/>
       <c r="D504" s="8"/>
       <c r="G504" s="9"/>
       <c r="H504" s="6"/>
     </row>
-    <row r="505" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="505" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B505" s="7"/>
       <c r="D505" s="8"/>
       <c r="G505" s="9"/>
       <c r="H505" s="6"/>
     </row>
-    <row r="506" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="506" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B506" s="7"/>
       <c r="D506" s="8"/>
       <c r="G506" s="9"/>
       <c r="H506" s="6"/>
     </row>
-    <row r="507" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="507" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B507" s="7"/>
       <c r="D507" s="8"/>
       <c r="G507" s="9"/>
       <c r="H507" s="6"/>
     </row>
-    <row r="508" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="508" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B508" s="7"/>
       <c r="D508" s="8"/>
       <c r="G508" s="9"/>
       <c r="H508" s="6"/>
     </row>
-    <row r="509" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="509" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B509" s="7"/>
       <c r="D509" s="8"/>
       <c r="G509" s="9"/>
       <c r="H509" s="6"/>
     </row>
-    <row r="510" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="510" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B510" s="7"/>
       <c r="D510" s="8"/>
       <c r="G510" s="9"/>
       <c r="H510" s="6"/>
     </row>
-    <row r="511" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="511" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B511" s="7"/>
       <c r="D511" s="8"/>
       <c r="G511" s="9"/>
       <c r="H511" s="6"/>
     </row>
-    <row r="512" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="512" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B512" s="7"/>
       <c r="D512" s="8"/>
       <c r="G512" s="9"/>
       <c r="H512" s="6"/>
     </row>
-    <row r="513" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="513" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B513" s="7"/>
       <c r="D513" s="8"/>
       <c r="G513" s="9"/>
       <c r="H513" s="6"/>
     </row>
-    <row r="514" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="514" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B514" s="7"/>
       <c r="D514" s="8"/>
       <c r="G514" s="9"/>
       <c r="H514" s="6"/>
     </row>
-    <row r="515" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="515" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B515" s="7"/>
       <c r="D515" s="8"/>
       <c r="G515" s="9"/>
       <c r="H515" s="6"/>
     </row>
-    <row r="516" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="516" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B516" s="7"/>
       <c r="D516" s="8"/>
       <c r="G516" s="9"/>
       <c r="H516" s="6"/>
     </row>
-    <row r="517" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="517" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B517" s="7"/>
       <c r="D517" s="8"/>
       <c r="G517" s="9"/>
       <c r="H517" s="6"/>
     </row>
-    <row r="518" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="518" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B518" s="7"/>
       <c r="D518" s="8"/>
       <c r="G518" s="9"/>
       <c r="H518" s="6"/>
     </row>
-    <row r="519" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="519" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B519" s="7"/>
       <c r="D519" s="8"/>
       <c r="G519" s="9"/>
       <c r="H519" s="6"/>
     </row>
-    <row r="520" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="520" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B520" s="7"/>
       <c r="D520" s="8"/>
       <c r="G520" s="9"/>
       <c r="H520" s="6"/>
     </row>
-    <row r="521" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="521" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B521" s="7"/>
       <c r="D521" s="8"/>
       <c r="G521" s="9"/>
       <c r="H521" s="6"/>
     </row>
-    <row r="522" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="522" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B522" s="7"/>
       <c r="D522" s="8"/>
       <c r="G522" s="9"/>
       <c r="H522" s="6"/>
     </row>
-    <row r="523" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="523" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B523" s="7"/>
       <c r="D523" s="8"/>
       <c r="G523" s="9"/>
       <c r="H523" s="6"/>
     </row>
-    <row r="524" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="524" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B524" s="7"/>
       <c r="D524" s="8"/>
       <c r="G524" s="9"/>
       <c r="H524" s="6"/>
     </row>
-    <row r="525" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="525" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B525" s="7"/>
       <c r="D525" s="8"/>
       <c r="G525" s="9"/>
       <c r="H525" s="6"/>
     </row>
-    <row r="526" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="526" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B526" s="7"/>
       <c r="D526" s="8"/>
       <c r="G526" s="9"/>
       <c r="H526" s="6"/>
     </row>
-    <row r="527" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="527" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B527" s="7"/>
       <c r="D527" s="8"/>
       <c r="G527" s="9"/>
       <c r="H527" s="6"/>
     </row>
-    <row r="528" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="528" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B528" s="7"/>
       <c r="D528" s="8"/>
       <c r="G528" s="9"/>
       <c r="H528" s="6"/>
     </row>
-    <row r="529" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="529" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B529" s="7"/>
       <c r="D529" s="8"/>
       <c r="G529" s="9"/>
       <c r="H529" s="6"/>
     </row>
-    <row r="530" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="530" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B530" s="7"/>
       <c r="D530" s="8"/>
       <c r="G530" s="9"/>
       <c r="H530" s="6"/>
     </row>
-    <row r="531" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="531" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B531" s="7"/>
       <c r="D531" s="8"/>
       <c r="G531" s="9"/>
       <c r="H531" s="6"/>
     </row>
-    <row r="532" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="532" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B532" s="7"/>
       <c r="D532" s="8"/>
       <c r="G532" s="9"/>
       <c r="H532" s="6"/>
     </row>
-    <row r="533" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="533" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B533" s="7"/>
       <c r="D533" s="8"/>
       <c r="G533" s="9"/>
       <c r="H533" s="6"/>
     </row>
-    <row r="534" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="534" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B534" s="7"/>
       <c r="D534" s="8"/>
       <c r="G534" s="9"/>
       <c r="H534" s="6"/>
     </row>
-    <row r="535" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="535" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B535" s="7"/>
       <c r="D535" s="8"/>
       <c r="G535" s="9"/>
       <c r="H535" s="6"/>
     </row>
-    <row r="536" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="536" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B536" s="7"/>
       <c r="D536" s="8"/>
       <c r="G536" s="9"/>
       <c r="H536" s="6"/>
     </row>
-    <row r="537" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="537" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B537" s="7"/>
       <c r="D537" s="8"/>
       <c r="G537" s="9"/>
       <c r="H537" s="6"/>
     </row>
-    <row r="538" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="538" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B538" s="7"/>
       <c r="D538" s="8"/>
       <c r="G538" s="9"/>
       <c r="H538" s="6"/>
     </row>
-    <row r="539" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="539" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B539" s="7"/>
       <c r="D539" s="8"/>
       <c r="G539" s="9"/>
       <c r="H539" s="6"/>
     </row>
-    <row r="540" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="540" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B540" s="7"/>
       <c r="D540" s="8"/>
       <c r="G540" s="9"/>
       <c r="H540" s="6"/>
     </row>
-    <row r="541" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="541" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B541" s="7"/>
       <c r="D541" s="8"/>
       <c r="G541" s="9"/>
       <c r="H541" s="6"/>
     </row>
-    <row r="542" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="542" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B542" s="7"/>
       <c r="D542" s="8"/>
       <c r="G542" s="9"/>
       <c r="H542" s="6"/>
     </row>
-    <row r="543" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="543" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B543" s="7"/>
       <c r="D543" s="8"/>
       <c r="G543" s="9"/>
       <c r="H543" s="6"/>
     </row>
-    <row r="544" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="544" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B544" s="7"/>
       <c r="D544" s="8"/>
       <c r="G544" s="9"/>
       <c r="H544" s="6"/>
     </row>
-    <row r="545" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="545" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B545" s="7"/>
       <c r="D545" s="8"/>
       <c r="G545" s="9"/>
       <c r="H545" s="6"/>
     </row>
-    <row r="546" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="546" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B546" s="7"/>
       <c r="D546" s="8"/>
       <c r="G546" s="9"/>
       <c r="H546" s="6"/>
     </row>
-    <row r="547" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="547" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B547" s="7"/>
       <c r="D547" s="8"/>
       <c r="G547" s="9"/>
       <c r="H547" s="6"/>
     </row>
-    <row r="548" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="548" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B548" s="7"/>
       <c r="D548" s="8"/>
       <c r="G548" s="9"/>
       <c r="H548" s="6"/>
     </row>
-    <row r="549" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="549" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B549" s="7"/>
       <c r="D549" s="8"/>
       <c r="G549" s="9"/>
       <c r="H549" s="6"/>
     </row>
-    <row r="550" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="550" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B550" s="7"/>
       <c r="D550" s="8"/>
       <c r="G550" s="9"/>
       <c r="H550" s="6"/>
     </row>
-    <row r="551" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="551" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B551" s="7"/>
       <c r="D551" s="8"/>
       <c r="G551" s="9"/>
       <c r="H551" s="6"/>
     </row>
-    <row r="552" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="552" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B552" s="7"/>
       <c r="D552" s="8"/>
       <c r="G552" s="9"/>
       <c r="H552" s="6"/>
     </row>
-    <row r="553" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="553" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B553" s="7"/>
       <c r="D553" s="8"/>
       <c r="G553" s="9"/>
       <c r="H553" s="6"/>
     </row>
-    <row r="554" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="554" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B554" s="7"/>
       <c r="D554" s="8"/>
       <c r="G554" s="9"/>
       <c r="H554" s="6"/>
     </row>
-    <row r="555" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="555" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B555" s="7"/>
       <c r="D555" s="8"/>
       <c r="G555" s="9"/>
       <c r="H555" s="6"/>
     </row>
-    <row r="556" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="556" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B556" s="7"/>
       <c r="D556" s="8"/>
       <c r="G556" s="9"/>
       <c r="H556" s="6"/>
     </row>
-    <row r="557" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="557" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B557" s="7"/>
       <c r="D557" s="8"/>
       <c r="G557" s="9"/>
       <c r="H557" s="6"/>
     </row>
-    <row r="558" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="558" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B558" s="7"/>
       <c r="D558" s="8"/>
       <c r="G558" s="9"/>
       <c r="H558" s="6"/>
     </row>
-    <row r="559" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="559" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B559" s="7"/>
       <c r="D559" s="8"/>
       <c r="G559" s="9"/>
       <c r="H559" s="6"/>
     </row>
-    <row r="560" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="560" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B560" s="7"/>
       <c r="D560" s="8"/>
       <c r="G560" s="9"/>
       <c r="H560" s="6"/>
     </row>
-    <row r="561" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="561" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B561" s="7"/>
       <c r="D561" s="8"/>
       <c r="G561" s="9"/>
       <c r="H561" s="6"/>
     </row>
-    <row r="562" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="562" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B562" s="7"/>
       <c r="D562" s="8"/>
       <c r="G562" s="9"/>
       <c r="H562" s="6"/>
     </row>
-    <row r="563" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="563" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B563" s="7"/>
       <c r="D563" s="8"/>
       <c r="G563" s="9"/>
       <c r="H563" s="6"/>
     </row>
-    <row r="564" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="564" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B564" s="7"/>
       <c r="D564" s="8"/>
       <c r="G564" s="9"/>
       <c r="H564" s="6"/>
     </row>
-    <row r="565" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="565" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B565" s="7"/>
       <c r="D565" s="8"/>
       <c r="G565" s="9"/>
       <c r="H565" s="6"/>
     </row>
-    <row r="566" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="566" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B566" s="7"/>
       <c r="D566" s="8"/>
       <c r="G566" s="9"/>
       <c r="H566" s="6"/>
     </row>
-    <row r="567" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="567" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B567" s="7"/>
       <c r="D567" s="8"/>
       <c r="G567" s="9"/>
       <c r="H567" s="6"/>
     </row>
-    <row r="568" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="568" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B568" s="7"/>
       <c r="D568" s="8"/>
       <c r="G568" s="9"/>
       <c r="H568" s="6"/>
     </row>
-    <row r="569" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="569" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B569" s="7"/>
       <c r="D569" s="8"/>
       <c r="G569" s="9"/>
       <c r="H569" s="6"/>
     </row>
-    <row r="570" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="570" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B570" s="7"/>
       <c r="D570" s="8"/>
       <c r="G570" s="9"/>
       <c r="H570" s="6"/>
     </row>
-    <row r="571" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="571" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B571" s="7"/>
       <c r="D571" s="8"/>
       <c r="G571" s="9"/>
       <c r="H571" s="6"/>
     </row>
-    <row r="572" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="572" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B572" s="7"/>
       <c r="D572" s="8"/>
       <c r="G572" s="9"/>
       <c r="H572" s="6"/>
     </row>
-    <row r="573" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="573" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B573" s="7"/>
       <c r="D573" s="8"/>
       <c r="G573" s="9"/>
       <c r="H573" s="6"/>
     </row>
-    <row r="574" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="574" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B574" s="7"/>
       <c r="D574" s="8"/>
       <c r="G574" s="9"/>
       <c r="H574" s="6"/>
     </row>
-    <row r="575" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="575" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B575" s="7"/>
       <c r="D575" s="8"/>
       <c r="G575" s="9"/>
       <c r="H575" s="6"/>
     </row>
-    <row r="576" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="576" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B576" s="7"/>
       <c r="D576" s="8"/>
       <c r="G576" s="9"/>
       <c r="H576" s="6"/>
     </row>
-    <row r="577" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="577" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B577" s="7"/>
       <c r="D577" s="8"/>
       <c r="G577" s="9"/>
       <c r="H577" s="6"/>
     </row>
-    <row r="578" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="578" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B578" s="7"/>
       <c r="D578" s="8"/>
       <c r="G578" s="9"/>
       <c r="H578" s="6"/>
     </row>
-    <row r="579" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="579" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B579" s="7"/>
       <c r="D579" s="8"/>
       <c r="G579" s="9"/>
       <c r="H579" s="6"/>
     </row>
-    <row r="580" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="580" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B580" s="7"/>
       <c r="D580" s="8"/>
       <c r="G580" s="9"/>
       <c r="H580" s="6"/>
     </row>
-    <row r="581" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="581" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B581" s="7"/>
       <c r="D581" s="8"/>
       <c r="G581" s="9"/>
       <c r="H581" s="6"/>
     </row>
-    <row r="582" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="582" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B582" s="7"/>
       <c r="D582" s="8"/>
       <c r="G582" s="9"/>
       <c r="H582" s="6"/>
     </row>
-    <row r="583" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="583" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B583" s="7"/>
       <c r="D583" s="8"/>
       <c r="G583" s="9"/>
       <c r="H583" s="6"/>
     </row>
-    <row r="584" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="584" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B584" s="7"/>
       <c r="D584" s="8"/>
       <c r="G584" s="9"/>
       <c r="H584" s="6"/>
     </row>
-    <row r="585" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="585" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B585" s="7"/>
       <c r="D585" s="8"/>
       <c r="G585" s="9"/>
       <c r="H585" s="6"/>
     </row>
-    <row r="586" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="586" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B586" s="7"/>
       <c r="D586" s="8"/>
       <c r="G586" s="9"/>
       <c r="H586" s="6"/>
     </row>
-    <row r="587" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="587" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B587" s="7"/>
       <c r="D587" s="8"/>
       <c r="G587" s="9"/>
       <c r="H587" s="6"/>
     </row>
-    <row r="588" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="588" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B588" s="7"/>
       <c r="D588" s="8"/>
       <c r="G588" s="9"/>
       <c r="H588" s="6"/>
     </row>
-    <row r="589" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="589" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B589" s="7"/>
       <c r="D589" s="8"/>
       <c r="G589" s="9"/>
       <c r="H589" s="6"/>
     </row>
-    <row r="590" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="590" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B590" s="7"/>
       <c r="D590" s="8"/>
       <c r="G590" s="9"/>
       <c r="H590" s="6"/>
     </row>
-    <row r="591" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="591" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B591" s="7"/>
       <c r="D591" s="8"/>
       <c r="G591" s="9"/>
       <c r="H591" s="6"/>
     </row>
-    <row r="592" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="592" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B592" s="7"/>
       <c r="D592" s="8"/>
       <c r="G592" s="9"/>
       <c r="H592" s="6"/>
     </row>
-    <row r="593" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="593" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B593" s="7"/>
       <c r="D593" s="8"/>
       <c r="G593" s="9"/>
       <c r="H593" s="6"/>
     </row>
-    <row r="594" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="594" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B594" s="7"/>
       <c r="D594" s="8"/>
       <c r="G594" s="9"/>
       <c r="H594" s="6"/>
     </row>
-    <row r="595" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="595" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B595" s="7"/>
       <c r="D595" s="8"/>
       <c r="G595" s="9"/>
       <c r="H595" s="6"/>
     </row>
-    <row r="596" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="596" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B596" s="7"/>
       <c r="D596" s="8"/>
       <c r="G596" s="9"/>
       <c r="H596" s="6"/>
     </row>
-    <row r="597" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="597" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B597" s="7"/>
       <c r="D597" s="8"/>
       <c r="G597" s="9"/>
       <c r="H597" s="6"/>
     </row>
-    <row r="598" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="598" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B598" s="7"/>
       <c r="D598" s="8"/>
       <c r="G598" s="9"/>
       <c r="H598" s="6"/>
     </row>
-    <row r="599" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="599" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B599" s="7"/>
       <c r="D599" s="8"/>
       <c r="G599" s="9"/>
       <c r="H599" s="6"/>
     </row>
-    <row r="600" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="600" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B600" s="7"/>
       <c r="D600" s="8"/>
       <c r="G600" s="9"/>
       <c r="H600" s="6"/>
     </row>
-    <row r="601" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="601" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B601" s="7"/>
       <c r="D601" s="8"/>
       <c r="G601" s="9"/>
       <c r="H601" s="6"/>
     </row>
-    <row r="602" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="602" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B602" s="7"/>
       <c r="D602" s="8"/>
       <c r="G602" s="9"/>
       <c r="H602" s="6"/>
     </row>
-    <row r="603" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="603" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B603" s="7"/>
       <c r="D603" s="8"/>
       <c r="G603" s="9"/>
       <c r="H603" s="6"/>
     </row>
-    <row r="604" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="604" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B604" s="7"/>
       <c r="D604" s="8"/>
       <c r="G604" s="9"/>
       <c r="H604" s="6"/>
     </row>
-    <row r="605" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="605" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B605" s="7"/>
       <c r="D605" s="8"/>
       <c r="G605" s="9"/>
       <c r="H605" s="6"/>
     </row>
-    <row r="606" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="606" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B606" s="7"/>
       <c r="D606" s="8"/>
       <c r="G606" s="9"/>
       <c r="H606" s="6"/>
     </row>
-    <row r="607" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="607" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B607" s="7"/>
       <c r="D607" s="8"/>
       <c r="G607" s="9"/>
       <c r="H607" s="6"/>
     </row>
-    <row r="608" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="608" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B608" s="7"/>
       <c r="D608" s="8"/>
       <c r="G608" s="9"/>
       <c r="H608" s="6"/>
     </row>
-    <row r="609" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="609" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B609" s="7"/>
       <c r="D609" s="8"/>
       <c r="G609" s="9"/>
       <c r="H609" s="6"/>
     </row>
-    <row r="610" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="610" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B610" s="7"/>
       <c r="D610" s="8"/>
       <c r="G610" s="9"/>
       <c r="H610" s="6"/>
     </row>
-    <row r="611" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="611" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B611" s="7"/>
       <c r="D611" s="8"/>
       <c r="G611" s="9"/>
       <c r="H611" s="6"/>
     </row>
-    <row r="612" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="612" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B612" s="7"/>
       <c r="D612" s="8"/>
       <c r="G612" s="9"/>
       <c r="H612" s="6"/>
     </row>
-    <row r="613" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="613" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B613" s="7"/>
       <c r="D613" s="8"/>
       <c r="G613" s="9"/>
       <c r="H613" s="6"/>
     </row>
-    <row r="614" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="614" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B614" s="7"/>
       <c r="D614" s="8"/>
       <c r="G614" s="9"/>
       <c r="H614" s="6"/>
     </row>
-    <row r="615" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="615" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B615" s="7"/>
       <c r="D615" s="8"/>
       <c r="G615" s="9"/>
       <c r="H615" s="6"/>
     </row>
-    <row r="616" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="616" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B616" s="7"/>
       <c r="D616" s="8"/>
       <c r="G616" s="9"/>
       <c r="H616" s="6"/>
     </row>
-    <row r="617" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="617" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B617" s="7"/>
       <c r="D617" s="8"/>
       <c r="G617" s="9"/>
       <c r="H617" s="6"/>
     </row>
-    <row r="618" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="618" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B618" s="7"/>
       <c r="D618" s="8"/>
       <c r="G618" s="9"/>
       <c r="H618" s="6"/>
     </row>
-    <row r="619" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="619" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B619" s="7"/>
       <c r="D619" s="8"/>
       <c r="G619" s="9"/>
       <c r="H619" s="6"/>
     </row>
-    <row r="620" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="620" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B620" s="7"/>
       <c r="D620" s="8"/>
       <c r="G620" s="9"/>
       <c r="H620" s="6"/>
     </row>
-    <row r="621" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="621" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B621" s="7"/>
       <c r="D621" s="8"/>
       <c r="G621" s="9"/>
       <c r="H621" s="6"/>
     </row>
-    <row r="622" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="622" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B622" s="7"/>
       <c r="D622" s="8"/>
       <c r="G622" s="9"/>
       <c r="H622" s="6"/>
     </row>
-    <row r="623" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="623" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B623" s="7"/>
       <c r="D623" s="8"/>
       <c r="G623" s="9"/>
       <c r="H623" s="6"/>
     </row>
-    <row r="624" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="624" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B624" s="7"/>
       <c r="D624" s="8"/>
       <c r="G624" s="9"/>
       <c r="H624" s="6"/>
     </row>
-    <row r="625" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="625" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B625" s="7"/>
       <c r="D625" s="8"/>
       <c r="G625" s="9"/>
       <c r="H625" s="6"/>
     </row>
-    <row r="626" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="626" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B626" s="7"/>
       <c r="D626" s="8"/>
       <c r="G626" s="9"/>
       <c r="H626" s="6"/>
     </row>
-    <row r="627" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="627" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B627" s="7"/>
       <c r="D627" s="8"/>
       <c r="G627" s="9"/>
       <c r="H627" s="6"/>
     </row>
-    <row r="628" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="628" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B628" s="7"/>
       <c r="D628" s="8"/>
       <c r="G628" s="9"/>
       <c r="H628" s="6"/>
     </row>
-    <row r="629" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="629" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B629" s="7"/>
       <c r="D629" s="8"/>
       <c r="G629" s="9"/>
       <c r="H629" s="6"/>
     </row>
-    <row r="630" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="630" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B630" s="7"/>
       <c r="D630" s="8"/>
       <c r="G630" s="9"/>
       <c r="H630" s="6"/>
     </row>
-    <row r="631" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="631" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B631" s="7"/>
       <c r="D631" s="8"/>
       <c r="G631" s="9"/>
       <c r="H631" s="6"/>
     </row>
-    <row r="632" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="632" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B632" s="7"/>
       <c r="D632" s="8"/>
       <c r="G632" s="9"/>
       <c r="H632" s="6"/>
     </row>
-    <row r="633" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="633" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B633" s="7"/>
       <c r="D633" s="8"/>
       <c r="G633" s="9"/>
       <c r="H633" s="6"/>
     </row>
-    <row r="634" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="634" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B634" s="7"/>
       <c r="D634" s="8"/>
       <c r="G634" s="9"/>
       <c r="H634" s="6"/>
     </row>
-    <row r="635" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="635" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B635" s="7"/>
       <c r="D635" s="8"/>
       <c r="G635" s="9"/>
       <c r="H635" s="6"/>
     </row>
-    <row r="636" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="636" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B636" s="7"/>
       <c r="D636" s="8"/>
       <c r="G636" s="9"/>
       <c r="H636" s="6"/>
     </row>
-    <row r="637" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="637" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B637" s="7"/>
       <c r="D637" s="8"/>
       <c r="G637" s="9"/>
       <c r="H637" s="6"/>
     </row>
-    <row r="638" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="638" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B638" s="7"/>
       <c r="D638" s="8"/>
       <c r="G638" s="9"/>
       <c r="H638" s="6"/>
     </row>
-    <row r="639" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="639" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B639" s="7"/>
       <c r="D639" s="8"/>
       <c r="G639" s="9"/>
       <c r="H639" s="6"/>
     </row>
-    <row r="640" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="640" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B640" s="7"/>
       <c r="D640" s="8"/>
       <c r="G640" s="9"/>
       <c r="H640" s="6"/>
     </row>
-    <row r="641" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="641" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B641" s="7"/>
       <c r="D641" s="8"/>
       <c r="G641" s="9"/>
       <c r="H641" s="6"/>
     </row>
-    <row r="642" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="642" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B642" s="7"/>
       <c r="D642" s="8"/>
       <c r="G642" s="9"/>
       <c r="H642" s="6"/>
     </row>
-    <row r="643" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="643" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B643" s="7"/>
       <c r="D643" s="8"/>
       <c r="G643" s="9"/>
       <c r="H643" s="6"/>
     </row>
-    <row r="644" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="644" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B644" s="7"/>
       <c r="D644" s="8"/>
       <c r="G644" s="9"/>
       <c r="H644" s="6"/>
     </row>
-    <row r="645" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="645" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B645" s="7"/>
       <c r="D645" s="8"/>
       <c r="G645" s="9"/>
       <c r="H645" s="6"/>
     </row>
-    <row r="646" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="646" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B646" s="7"/>
       <c r="D646" s="8"/>
       <c r="G646" s="9"/>
       <c r="H646" s="6"/>
     </row>
-    <row r="647" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="647" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B647" s="7"/>
       <c r="D647" s="8"/>
       <c r="G647" s="9"/>
       <c r="H647" s="6"/>
     </row>
-    <row r="648" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="648" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B648" s="7"/>
       <c r="D648" s="8"/>
       <c r="G648" s="9"/>
       <c r="H648" s="6"/>
     </row>
-    <row r="649" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="649" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B649" s="7"/>
       <c r="D649" s="8"/>
       <c r="G649" s="9"/>
       <c r="H649" s="6"/>
     </row>
-    <row r="650" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="650" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B650" s="7"/>
       <c r="D650" s="8"/>
       <c r="G650" s="9"/>
       <c r="H650" s="6"/>
     </row>
-    <row r="651" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="651" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B651" s="7"/>
       <c r="D651" s="8"/>
       <c r="G651" s="9"/>
       <c r="H651" s="6"/>
     </row>
-    <row r="652" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="652" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B652" s="7"/>
       <c r="D652" s="8"/>
       <c r="G652" s="9"/>
       <c r="H652" s="6"/>
     </row>
-    <row r="653" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="653" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B653" s="7"/>
       <c r="D653" s="8"/>
       <c r="G653" s="9"/>
       <c r="H653" s="6"/>
     </row>
-    <row r="654" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="654" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B654" s="7"/>
       <c r="D654" s="8"/>
       <c r="G654" s="9"/>
       <c r="H654" s="6"/>
     </row>
-    <row r="655" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="655" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B655" s="7"/>
       <c r="D655" s="8"/>
       <c r="G655" s="9"/>
       <c r="H655" s="6"/>
     </row>
-    <row r="656" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="656" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B656" s="7"/>
       <c r="D656" s="8"/>
       <c r="G656" s="9"/>
       <c r="H656" s="6"/>
     </row>
-    <row r="657" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="657" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B657" s="7"/>
       <c r="D657" s="8"/>
       <c r="G657" s="9"/>
       <c r="H657" s="6"/>
     </row>
-    <row r="658" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="658" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B658" s="7"/>
       <c r="D658" s="8"/>
       <c r="G658" s="9"/>
       <c r="H658" s="6"/>
     </row>
-    <row r="659" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="659" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B659" s="7"/>
       <c r="D659" s="8"/>
       <c r="G659" s="9"/>
       <c r="H659" s="6"/>
     </row>
-    <row r="660" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="660" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B660" s="7"/>
       <c r="D660" s="8"/>
       <c r="G660" s="9"/>
       <c r="H660" s="6"/>
     </row>
-    <row r="661" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="661" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B661" s="7"/>
       <c r="D661" s="8"/>
       <c r="G661" s="9"/>
       <c r="H661" s="6"/>
     </row>
-    <row r="662" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="662" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B662" s="7"/>
       <c r="D662" s="8"/>
       <c r="G662" s="9"/>
       <c r="H662" s="6"/>
     </row>
-    <row r="663" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="663" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B663" s="7"/>
       <c r="D663" s="8"/>
       <c r="G663" s="9"/>
       <c r="H663" s="6"/>
     </row>
-    <row r="664" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="664" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B664" s="7"/>
       <c r="D664" s="8"/>
       <c r="G664" s="9"/>
       <c r="H664" s="6"/>
     </row>
-    <row r="665" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="665" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B665" s="7"/>
       <c r="D665" s="8"/>
       <c r="G665" s="9"/>
       <c r="H665" s="6"/>
     </row>
-    <row r="666" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="666" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B666" s="7"/>
       <c r="D666" s="8"/>
       <c r="G666" s="9"/>
       <c r="H666" s="6"/>
     </row>
-    <row r="667" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="667" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B667" s="7"/>
       <c r="D667" s="8"/>
       <c r="G667" s="9"/>
       <c r="H667" s="6"/>
     </row>
-    <row r="668" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="668" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B668" s="7"/>
       <c r="D668" s="8"/>
       <c r="G668" s="9"/>
       <c r="H668" s="6"/>
     </row>
-    <row r="669" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="669" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B669" s="7"/>
       <c r="D669" s="8"/>
       <c r="G669" s="9"/>
       <c r="H669" s="6"/>
     </row>
-    <row r="670" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="670" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B670" s="7"/>
       <c r="D670" s="8"/>
       <c r="G670" s="9"/>
       <c r="H670" s="6"/>
     </row>
-    <row r="671" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="671" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B671" s="7"/>
       <c r="D671" s="8"/>
       <c r="G671" s="9"/>
       <c r="H671" s="6"/>
     </row>
-    <row r="672" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="672" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B672" s="7"/>
       <c r="D672" s="8"/>
       <c r="G672" s="9"/>
       <c r="H672" s="6"/>
     </row>
-    <row r="673" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="673" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B673" s="7"/>
       <c r="D673" s="8"/>
       <c r="G673" s="9"/>
       <c r="H673" s="6"/>
     </row>
-    <row r="674" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="674" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B674" s="7"/>
       <c r="D674" s="8"/>
       <c r="G674" s="9"/>
       <c r="H674" s="6"/>
     </row>
-    <row r="675" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="675" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B675" s="7"/>
       <c r="D675" s="8"/>
       <c r="G675" s="9"/>
       <c r="H675" s="6"/>
     </row>
-    <row r="676" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="676" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B676" s="7"/>
       <c r="D676" s="8"/>
       <c r="G676" s="9"/>
       <c r="H676" s="6"/>
     </row>
-    <row r="677" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="677" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B677" s="7"/>
       <c r="D677" s="8"/>
       <c r="G677" s="9"/>
       <c r="H677" s="6"/>
     </row>
-    <row r="678" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="678" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B678" s="7"/>
       <c r="D678" s="8"/>
       <c r="G678" s="9"/>
       <c r="H678" s="6"/>
     </row>
-    <row r="679" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="679" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B679" s="7"/>
       <c r="D679" s="8"/>
       <c r="G679" s="9"/>
       <c r="H679" s="6"/>
     </row>
-    <row r="680" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="680" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B680" s="7"/>
       <c r="D680" s="8"/>
       <c r="G680" s="9"/>
       <c r="H680" s="6"/>
     </row>
-    <row r="681" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="681" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B681" s="7"/>
       <c r="D681" s="8"/>
       <c r="G681" s="9"/>
       <c r="H681" s="6"/>
     </row>
-    <row r="682" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="682" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B682" s="7"/>
       <c r="D682" s="8"/>
       <c r="G682" s="9"/>
       <c r="H682" s="6"/>
     </row>
-    <row r="683" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="683" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B683" s="7"/>
       <c r="D683" s="8"/>
       <c r="G683" s="9"/>
       <c r="H683" s="6"/>
     </row>
-    <row r="684" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="684" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B684" s="7"/>
       <c r="D684" s="8"/>
       <c r="G684" s="9"/>
       <c r="H684" s="6"/>
     </row>
-    <row r="685" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="685" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B685" s="7"/>
       <c r="D685" s="8"/>
       <c r="G685" s="9"/>
       <c r="H685" s="6"/>
     </row>
-    <row r="686" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="686" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B686" s="7"/>
       <c r="D686" s="8"/>
       <c r="G686" s="9"/>
       <c r="H686" s="6"/>
     </row>
-    <row r="687" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="687" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B687" s="7"/>
       <c r="D687" s="8"/>
       <c r="G687" s="9"/>
       <c r="H687" s="6"/>
     </row>
-    <row r="688" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="688" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B688" s="7"/>
       <c r="D688" s="8"/>
       <c r="G688" s="9"/>
       <c r="H688" s="6"/>
     </row>
-    <row r="689" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="689" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B689" s="7"/>
       <c r="D689" s="8"/>
       <c r="G689" s="9"/>
       <c r="H689" s="6"/>
     </row>
-    <row r="690" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="690" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B690" s="7"/>
       <c r="D690" s="8"/>
       <c r="G690" s="9"/>
       <c r="H690" s="6"/>
     </row>
-    <row r="691" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="691" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B691" s="7"/>
       <c r="D691" s="8"/>
       <c r="G691" s="9"/>
       <c r="H691" s="6"/>
     </row>
-    <row r="692" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="692" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B692" s="7"/>
       <c r="D692" s="8"/>
       <c r="G692" s="9"/>
       <c r="H692" s="6"/>
     </row>
-    <row r="693" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="693" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B693" s="7"/>
       <c r="D693" s="8"/>
       <c r="G693" s="9"/>
       <c r="H693" s="6"/>
     </row>
-    <row r="694" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="694" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B694" s="7"/>
       <c r="D694" s="8"/>
       <c r="G694" s="9"/>
       <c r="H694" s="6"/>
     </row>
-    <row r="695" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="695" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B695" s="7"/>
       <c r="D695" s="8"/>
       <c r="G695" s="9"/>
       <c r="H695" s="6"/>
     </row>
-    <row r="696" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="696" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B696" s="7"/>
       <c r="D696" s="8"/>
       <c r="G696" s="9"/>
       <c r="H696" s="6"/>
     </row>
-    <row r="697" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="697" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B697" s="7"/>
       <c r="D697" s="8"/>
       <c r="G697" s="9"/>
       <c r="H697" s="6"/>
     </row>
-    <row r="698" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="698" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B698" s="7"/>
       <c r="D698" s="8"/>
       <c r="G698" s="9"/>
       <c r="H698" s="6"/>
     </row>
-    <row r="699" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="699" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B699" s="7"/>
       <c r="D699" s="8"/>
       <c r="G699" s="9"/>
       <c r="H699" s="6"/>
     </row>
-    <row r="700" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="700" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B700" s="7"/>
       <c r="D700" s="8"/>
       <c r="G700" s="9"/>
       <c r="H700" s="6"/>
     </row>
-    <row r="701" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="701" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B701" s="7"/>
       <c r="D701" s="8"/>
       <c r="G701" s="9"/>
       <c r="H701" s="6"/>
     </row>
-    <row r="702" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="702" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B702" s="7"/>
       <c r="D702" s="8"/>
       <c r="G702" s="9"/>
       <c r="H702" s="6"/>
     </row>
-    <row r="703" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="703" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B703" s="7"/>
       <c r="D703" s="8"/>
       <c r="G703" s="9"/>
       <c r="H703" s="6"/>
     </row>
-    <row r="704" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="704" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B704" s="7"/>
       <c r="D704" s="8"/>
       <c r="G704" s="9"/>
       <c r="H704" s="6"/>
     </row>
-    <row r="705" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="705" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B705" s="7"/>
       <c r="D705" s="8"/>
       <c r="G705" s="9"/>
       <c r="H705" s="6"/>
     </row>
-    <row r="706" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="706" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B706" s="7"/>
       <c r="D706" s="8"/>
       <c r="G706" s="9"/>
       <c r="H706" s="6"/>
     </row>
-    <row r="707" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="707" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B707" s="7"/>
       <c r="D707" s="8"/>
       <c r="G707" s="9"/>
       <c r="H707" s="6"/>
     </row>
-    <row r="708" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="708" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B708" s="7"/>
       <c r="D708" s="8"/>
       <c r="G708" s="9"/>
       <c r="H708" s="6"/>
     </row>
-    <row r="709" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="709" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B709" s="7"/>
       <c r="D709" s="8"/>
       <c r="G709" s="9"/>
       <c r="H709" s="6"/>
     </row>
-    <row r="710" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="710" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B710" s="7"/>
       <c r="D710" s="8"/>
       <c r="G710" s="9"/>
       <c r="H710" s="6"/>
     </row>
-    <row r="711" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="711" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B711" s="7"/>
       <c r="D711" s="8"/>
       <c r="G711" s="9"/>
       <c r="H711" s="6"/>
     </row>
-    <row r="712" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="712" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B712" s="7"/>
       <c r="D712" s="8"/>
       <c r="G712" s="9"/>
       <c r="H712" s="6"/>
     </row>
-    <row r="713" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="713" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B713" s="7"/>
       <c r="D713" s="8"/>
       <c r="G713" s="9"/>
       <c r="H713" s="6"/>
     </row>
-    <row r="714" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="714" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B714" s="7"/>
       <c r="D714" s="8"/>
       <c r="G714" s="9"/>
       <c r="H714" s="6"/>
     </row>
-    <row r="715" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="715" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B715" s="7"/>
       <c r="D715" s="8"/>
       <c r="G715" s="9"/>
       <c r="H715" s="6"/>
     </row>
-    <row r="716" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="716" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B716" s="7"/>
       <c r="D716" s="8"/>
       <c r="G716" s="9"/>
       <c r="H716" s="6"/>
     </row>
-    <row r="717" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="717" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B717" s="7"/>
       <c r="D717" s="8"/>
       <c r="G717" s="9"/>
       <c r="H717" s="6"/>
     </row>
-    <row r="718" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="718" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B718" s="7"/>
       <c r="D718" s="8"/>
       <c r="G718" s="9"/>
       <c r="H718" s="6"/>
     </row>
-    <row r="719" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="719" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B719" s="7"/>
       <c r="D719" s="8"/>
       <c r="G719" s="9"/>
       <c r="H719" s="6"/>
     </row>
-    <row r="720" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="720" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B720" s="7"/>
       <c r="D720" s="8"/>
       <c r="G720" s="9"/>
       <c r="H720" s="6"/>
     </row>
-    <row r="721" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="721" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B721" s="7"/>
       <c r="D721" s="8"/>
       <c r="G721" s="9"/>
       <c r="H721" s="6"/>
     </row>
-    <row r="722" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="722" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B722" s="7"/>
       <c r="D722" s="8"/>
       <c r="G722" s="9"/>
       <c r="H722" s="6"/>
     </row>
-    <row r="723" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="723" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B723" s="7"/>
       <c r="D723" s="8"/>
       <c r="G723" s="9"/>
       <c r="H723" s="6"/>
     </row>
-    <row r="724" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="724" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B724" s="7"/>
       <c r="D724" s="8"/>
       <c r="G724" s="9"/>
       <c r="H724" s="6"/>
     </row>
-    <row r="725" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="725" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B725" s="7"/>
       <c r="D725" s="8"/>
       <c r="G725" s="9"/>
       <c r="H725" s="6"/>
     </row>
-    <row r="726" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="726" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B726" s="7"/>
       <c r="D726" s="8"/>
       <c r="G726" s="9"/>
       <c r="H726" s="6"/>
     </row>
-    <row r="727" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="727" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B727" s="7"/>
       <c r="D727" s="8"/>
       <c r="G727" s="9"/>
       <c r="H727" s="6"/>
     </row>
-    <row r="728" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="728" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B728" s="7"/>
       <c r="D728" s="8"/>
       <c r="G728" s="9"/>
       <c r="H728" s="6"/>
     </row>
-    <row r="729" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="729" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B729" s="7"/>
       <c r="D729" s="8"/>
       <c r="G729" s="9"/>
       <c r="H729" s="6"/>
     </row>
-    <row r="730" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="730" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B730" s="7"/>
       <c r="D730" s="8"/>
       <c r="G730" s="9"/>
       <c r="H730" s="6"/>
     </row>
-    <row r="731" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="731" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B731" s="7"/>
       <c r="D731" s="8"/>
       <c r="G731" s="9"/>
       <c r="H731" s="6"/>
     </row>
-    <row r="732" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="732" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B732" s="7"/>
       <c r="D732" s="8"/>
       <c r="G732" s="9"/>
       <c r="H732" s="6"/>
     </row>
-    <row r="733" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="733" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B733" s="7"/>
       <c r="D733" s="8"/>
       <c r="G733" s="9"/>
       <c r="H733" s="6"/>
     </row>
-    <row r="734" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="734" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B734" s="7"/>
       <c r="D734" s="8"/>
       <c r="G734" s="9"/>
       <c r="H734" s="6"/>
     </row>
-    <row r="735" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="735" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B735" s="7"/>
       <c r="D735" s="8"/>
       <c r="G735" s="9"/>
       <c r="H735" s="6"/>
     </row>
-    <row r="736" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="736" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B736" s="7"/>
       <c r="D736" s="8"/>
       <c r="G736" s="9"/>
       <c r="H736" s="6"/>
     </row>
-    <row r="737" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="737" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B737" s="7"/>
       <c r="D737" s="8"/>
       <c r="G737" s="9"/>
       <c r="H737" s="6"/>
     </row>
-    <row r="738" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="738" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B738" s="7"/>
       <c r="D738" s="8"/>
       <c r="G738" s="9"/>
       <c r="H738" s="6"/>
     </row>
-    <row r="739" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="739" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B739" s="7"/>
       <c r="D739" s="8"/>
       <c r="G739" s="9"/>
       <c r="H739" s="6"/>
     </row>
-    <row r="740" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="740" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B740" s="7"/>
       <c r="D740" s="8"/>
       <c r="G740" s="9"/>
       <c r="H740" s="6"/>
     </row>
-    <row r="741" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="741" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B741" s="7"/>
       <c r="D741" s="8"/>
       <c r="G741" s="9"/>
       <c r="H741" s="6"/>
     </row>
-    <row r="742" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="742" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B742" s="7"/>
       <c r="D742" s="8"/>
       <c r="G742" s="9"/>
       <c r="H742" s="6"/>
     </row>
-    <row r="743" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="743" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B743" s="7"/>
       <c r="D743" s="8"/>
       <c r="G743" s="9"/>
       <c r="H743" s="6"/>
     </row>
-    <row r="744" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="744" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B744" s="7"/>
       <c r="D744" s="8"/>
       <c r="G744" s="9"/>
       <c r="H744" s="6"/>
     </row>
-    <row r="745" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="745" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B745" s="7"/>
       <c r="D745" s="8"/>
       <c r="G745" s="9"/>
       <c r="H745" s="6"/>
     </row>
-    <row r="746" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="746" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B746" s="7"/>
       <c r="D746" s="8"/>
       <c r="G746" s="9"/>
       <c r="H746" s="6"/>
     </row>
-    <row r="747" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="747" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B747" s="7"/>
       <c r="D747" s="8"/>
       <c r="G747" s="9"/>
       <c r="H747" s="6"/>
     </row>
-    <row r="748" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="748" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B748" s="7"/>
       <c r="D748" s="8"/>
       <c r="G748" s="9"/>
       <c r="H748" s="6"/>
     </row>
-    <row r="749" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="749" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B749" s="7"/>
       <c r="D749" s="8"/>
       <c r="G749" s="9"/>
       <c r="H749" s="6"/>
     </row>
-    <row r="750" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="750" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B750" s="7"/>
       <c r="D750" s="8"/>
       <c r="G750" s="9"/>
       <c r="H750" s="6"/>
     </row>
-    <row r="751" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="751" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B751" s="7"/>
       <c r="D751" s="8"/>
       <c r="G751" s="9"/>
       <c r="H751" s="6"/>
     </row>
-    <row r="752" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="752" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B752" s="7"/>
       <c r="D752" s="8"/>
       <c r="G752" s="9"/>
       <c r="H752" s="6"/>
     </row>
-    <row r="753" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="753" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B753" s="7"/>
       <c r="D753" s="8"/>
       <c r="G753" s="9"/>
       <c r="H753" s="6"/>
     </row>
-    <row r="754" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="754" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B754" s="7"/>
       <c r="D754" s="8"/>
       <c r="G754" s="9"/>
       <c r="H754" s="6"/>
     </row>
-    <row r="755" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="755" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B755" s="7"/>
       <c r="D755" s="8"/>
       <c r="G755" s="9"/>
       <c r="H755" s="6"/>
     </row>
-    <row r="756" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="756" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B756" s="7"/>
       <c r="D756" s="8"/>
       <c r="G756" s="9"/>
       <c r="H756" s="6"/>
     </row>
-    <row r="757" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="757" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B757" s="7"/>
       <c r="D757" s="8"/>
       <c r="G757" s="9"/>
       <c r="H757" s="6"/>
     </row>
-    <row r="758" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="758" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B758" s="7"/>
       <c r="D758" s="8"/>
       <c r="G758" s="9"/>
       <c r="H758" s="6"/>
     </row>
-    <row r="759" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="759" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B759" s="7"/>
       <c r="D759" s="8"/>
       <c r="G759" s="9"/>
       <c r="H759" s="6"/>
     </row>
-    <row r="760" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="760" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B760" s="7"/>
       <c r="D760" s="8"/>
       <c r="G760" s="9"/>
       <c r="H760" s="6"/>
     </row>
-    <row r="761" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="761" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B761" s="7"/>
       <c r="D761" s="8"/>
       <c r="G761" s="9"/>
       <c r="H761" s="6"/>
     </row>
-    <row r="762" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="762" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B762" s="7"/>
       <c r="D762" s="8"/>
       <c r="G762" s="9"/>
       <c r="H762" s="6"/>
     </row>
-    <row r="763" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="763" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B763" s="7"/>
       <c r="D763" s="8"/>
       <c r="G763" s="9"/>
       <c r="H763" s="6"/>
     </row>
-    <row r="764" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="764" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B764" s="7"/>
       <c r="D764" s="8"/>
       <c r="G764" s="9"/>
       <c r="H764" s="6"/>
     </row>
-    <row r="765" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="765" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B765" s="7"/>
       <c r="D765" s="8"/>
       <c r="G765" s="9"/>
       <c r="H765" s="6"/>
     </row>
-    <row r="766" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="766" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B766" s="7"/>
       <c r="D766" s="8"/>
       <c r="G766" s="9"/>
       <c r="H766" s="6"/>
     </row>
-    <row r="767" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="767" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B767" s="7"/>
       <c r="D767" s="8"/>
       <c r="G767" s="9"/>
       <c r="H767" s="6"/>
     </row>
-    <row r="768" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="768" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B768" s="7"/>
       <c r="D768" s="8"/>
       <c r="G768" s="9"/>
       <c r="H768" s="6"/>
     </row>
-    <row r="769" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="769" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B769" s="7"/>
       <c r="D769" s="8"/>
       <c r="G769" s="9"/>
       <c r="H769" s="6"/>
     </row>
-    <row r="770" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="770" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B770" s="7"/>
       <c r="D770" s="8"/>
       <c r="G770" s="9"/>
       <c r="H770" s="6"/>
     </row>
-    <row r="771" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="771" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B771" s="7"/>
       <c r="D771" s="8"/>
       <c r="G771" s="9"/>
       <c r="H771" s="6"/>
     </row>
-    <row r="772" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="772" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B772" s="7"/>
       <c r="D772" s="8"/>
       <c r="G772" s="9"/>
       <c r="H772" s="6"/>
     </row>
-    <row r="773" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="773" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B773" s="7"/>
       <c r="D773" s="8"/>
       <c r="G773" s="9"/>
       <c r="H773" s="6"/>
     </row>
-    <row r="774" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="774" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B774" s="7"/>
       <c r="D774" s="8"/>
       <c r="G774" s="9"/>
       <c r="H774" s="6"/>
     </row>
-    <row r="775" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="775" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B775" s="7"/>
       <c r="D775" s="8"/>
       <c r="G775" s="9"/>
       <c r="H775" s="6"/>
     </row>
-    <row r="776" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="776" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B776" s="7"/>
       <c r="D776" s="8"/>
       <c r="G776" s="9"/>
       <c r="H776" s="6"/>
     </row>
-    <row r="777" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="777" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B777" s="7"/>
       <c r="D777" s="8"/>
       <c r="G777" s="9"/>
       <c r="H777" s="6"/>
     </row>
-    <row r="778" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="778" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B778" s="7"/>
       <c r="D778" s="8"/>
       <c r="G778" s="9"/>
       <c r="H778" s="6"/>
     </row>
-    <row r="779" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="779" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B779" s="7"/>
       <c r="D779" s="8"/>
       <c r="G779" s="9"/>
       <c r="H779" s="6"/>
     </row>
-    <row r="780" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="780" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B780" s="7"/>
       <c r="D780" s="8"/>
       <c r="G780" s="9"/>
       <c r="H780" s="6"/>
     </row>
-    <row r="781" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="781" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B781" s="7"/>
       <c r="D781" s="8"/>
       <c r="G781" s="9"/>
       <c r="H781" s="6"/>
     </row>
-    <row r="782" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="782" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B782" s="7"/>
       <c r="D782" s="8"/>
       <c r="G782" s="9"/>
       <c r="H782" s="6"/>
     </row>
-    <row r="783" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="783" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B783" s="7"/>
       <c r="D783" s="8"/>
       <c r="G783" s="9"/>
       <c r="H783" s="6"/>
     </row>
-    <row r="784" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="784" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B784" s="7"/>
       <c r="D784" s="8"/>
       <c r="G784" s="9"/>
       <c r="H784" s="6"/>
     </row>
-    <row r="785" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="785" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B785" s="7"/>
       <c r="D785" s="8"/>
       <c r="G785" s="9"/>
       <c r="H785" s="6"/>
     </row>
-    <row r="786" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="786" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B786" s="7"/>
       <c r="D786" s="8"/>
       <c r="G786" s="9"/>
       <c r="H786" s="6"/>
     </row>
-    <row r="787" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="787" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B787" s="7"/>
       <c r="D787" s="8"/>
       <c r="G787" s="9"/>
       <c r="H787" s="6"/>
     </row>
-    <row r="788" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="788" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B788" s="7"/>
       <c r="D788" s="8"/>
       <c r="G788" s="9"/>
       <c r="H788" s="6"/>
     </row>
-    <row r="789" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="789" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B789" s="7"/>
       <c r="D789" s="8"/>
       <c r="G789" s="9"/>
       <c r="H789" s="6"/>
     </row>
-    <row r="790" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="790" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B790" s="7"/>
       <c r="D790" s="8"/>
       <c r="G790" s="9"/>
       <c r="H790" s="6"/>
     </row>
-    <row r="791" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="791" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B791" s="7"/>
       <c r="D791" s="8"/>
       <c r="G791" s="9"/>
       <c r="H791" s="6"/>
     </row>
-    <row r="792" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="792" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B792" s="7"/>
       <c r="D792" s="8"/>
       <c r="G792" s="9"/>
       <c r="H792" s="6"/>
     </row>
-    <row r="793" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="793" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B793" s="7"/>
       <c r="D793" s="8"/>
       <c r="G793" s="9"/>
       <c r="H793" s="6"/>
     </row>
-    <row r="794" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="794" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B794" s="7"/>
       <c r="D794" s="8"/>
       <c r="G794" s="9"/>
       <c r="H794" s="6"/>
     </row>
-    <row r="795" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="795" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B795" s="7"/>
       <c r="D795" s="8"/>
       <c r="G795" s="9"/>
       <c r="H795" s="6"/>
     </row>
-    <row r="796" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="796" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B796" s="7"/>
       <c r="D796" s="8"/>
       <c r="G796" s="9"/>
       <c r="H796" s="6"/>
     </row>
-    <row r="797" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="797" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B797" s="7"/>
       <c r="D797" s="8"/>
       <c r="G797" s="9"/>
       <c r="H797" s="6"/>
     </row>
-    <row r="798" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="798" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B798" s="7"/>
       <c r="D798" s="8"/>
       <c r="G798" s="9"/>
       <c r="H798" s="6"/>
     </row>
-    <row r="799" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="799" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B799" s="7"/>
       <c r="D799" s="8"/>
       <c r="G799" s="9"/>
       <c r="H799" s="6"/>
     </row>
-    <row r="800" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="800" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B800" s="7"/>
       <c r="D800" s="8"/>
       <c r="G800" s="9"/>
       <c r="H800" s="6"/>
     </row>
-    <row r="801" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="801" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B801" s="7"/>
       <c r="D801" s="8"/>
       <c r="G801" s="9"/>
       <c r="H801" s="6"/>
     </row>
-    <row r="802" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="802" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B802" s="7"/>
       <c r="D802" s="8"/>
       <c r="G802" s="9"/>
       <c r="H802" s="6"/>
     </row>
-    <row r="803" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="803" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B803" s="7"/>
       <c r="D803" s="8"/>
       <c r="G803" s="9"/>
       <c r="H803" s="6"/>
     </row>
-    <row r="804" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="804" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B804" s="7"/>
       <c r="D804" s="8"/>
       <c r="G804" s="9"/>
       <c r="H804" s="6"/>
     </row>
-    <row r="805" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="805" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B805" s="7"/>
       <c r="D805" s="8"/>
       <c r="G805" s="9"/>
       <c r="H805" s="6"/>
     </row>
-    <row r="806" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="806" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B806" s="7"/>
       <c r="D806" s="8"/>
       <c r="G806" s="9"/>
       <c r="H806" s="6"/>
     </row>
-    <row r="807" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="807" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B807" s="7"/>
       <c r="D807" s="8"/>
       <c r="G807" s="9"/>
       <c r="H807" s="6"/>
     </row>
-    <row r="808" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="808" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B808" s="7"/>
       <c r="D808" s="8"/>
       <c r="G808" s="9"/>
       <c r="H808" s="6"/>
     </row>
-    <row r="809" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="809" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B809" s="7"/>
       <c r="D809" s="8"/>
       <c r="G809" s="9"/>
       <c r="H809" s="6"/>
     </row>
-    <row r="810" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="810" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B810" s="7"/>
       <c r="D810" s="8"/>
       <c r="G810" s="9"/>
       <c r="H810" s="6"/>
     </row>
-    <row r="811" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="811" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B811" s="7"/>
       <c r="D811" s="8"/>
       <c r="G811" s="9"/>
       <c r="H811" s="6"/>
     </row>
-    <row r="812" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="812" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B812" s="7"/>
       <c r="D812" s="8"/>
       <c r="G812" s="9"/>
       <c r="H812" s="6"/>
     </row>
-    <row r="813" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="813" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B813" s="7"/>
       <c r="D813" s="8"/>
       <c r="G813" s="9"/>
       <c r="H813" s="6"/>
     </row>
-    <row r="814" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="814" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B814" s="7"/>
       <c r="D814" s="8"/>
       <c r="G814" s="9"/>
       <c r="H814" s="6"/>
     </row>
-    <row r="815" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="815" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B815" s="7"/>
       <c r="D815" s="8"/>
       <c r="G815" s="9"/>
       <c r="H815" s="6"/>
     </row>
-    <row r="816" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="816" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B816" s="7"/>
       <c r="D816" s="8"/>
       <c r="G816" s="9"/>
       <c r="H816" s="6"/>
     </row>
-    <row r="817" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="817" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B817" s="7"/>
       <c r="D817" s="8"/>
       <c r="G817" s="9"/>
       <c r="H817" s="6"/>
     </row>
-    <row r="818" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="818" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B818" s="7"/>
       <c r="D818" s="8"/>
       <c r="G818" s="9"/>
       <c r="H818" s="6"/>
     </row>
-    <row r="819" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="819" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B819" s="7"/>
       <c r="D819" s="8"/>
       <c r="G819" s="9"/>
       <c r="H819" s="6"/>
     </row>
-    <row r="820" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="820" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B820" s="7"/>
       <c r="D820" s="8"/>
       <c r="G820" s="9"/>
       <c r="H820" s="6"/>
     </row>
-    <row r="821" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="821" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B821" s="7"/>
       <c r="D821" s="8"/>
       <c r="G821" s="9"/>
       <c r="H821" s="6"/>
     </row>
-    <row r="822" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="822" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B822" s="7"/>
       <c r="D822" s="8"/>
       <c r="G822" s="9"/>
       <c r="H822" s="6"/>
     </row>
-    <row r="823" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="823" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B823" s="7"/>
       <c r="D823" s="8"/>
       <c r="G823" s="9"/>
       <c r="H823" s="6"/>
     </row>
-    <row r="824" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="824" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B824" s="7"/>
       <c r="D824" s="8"/>
       <c r="G824" s="9"/>
       <c r="H824" s="6"/>
     </row>
-    <row r="825" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="825" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B825" s="7"/>
       <c r="D825" s="8"/>
       <c r="G825" s="9"/>
       <c r="H825" s="6"/>
     </row>
-    <row r="826" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="826" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B826" s="7"/>
       <c r="D826" s="8"/>
       <c r="G826" s="9"/>
       <c r="H826" s="6"/>
     </row>
-    <row r="827" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="827" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B827" s="7"/>
       <c r="D827" s="8"/>
       <c r="G827" s="9"/>
       <c r="H827" s="6"/>
     </row>
-    <row r="828" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="828" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B828" s="7"/>
       <c r="D828" s="8"/>
       <c r="G828" s="9"/>
       <c r="H828" s="6"/>
     </row>
-    <row r="829" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="829" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B829" s="7"/>
       <c r="D829" s="8"/>
       <c r="G829" s="9"/>
       <c r="H829" s="6"/>
     </row>
-    <row r="830" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="830" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B830" s="7"/>
       <c r="D830" s="8"/>
       <c r="G830" s="9"/>
       <c r="H830" s="6"/>
     </row>
-    <row r="831" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="831" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B831" s="7"/>
       <c r="D831" s="8"/>
       <c r="G831" s="9"/>
       <c r="H831" s="6"/>
     </row>
-    <row r="832" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="832" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B832" s="7"/>
       <c r="D832" s="8"/>
       <c r="G832" s="9"/>
       <c r="H832" s="6"/>
     </row>
-    <row r="833" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="833" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B833" s="7"/>
       <c r="D833" s="8"/>
       <c r="G833" s="9"/>
       <c r="H833" s="6"/>
     </row>
-    <row r="834" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="834" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B834" s="7"/>
       <c r="D834" s="8"/>
       <c r="G834" s="9"/>
       <c r="H834" s="6"/>
     </row>
-    <row r="835" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="835" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B835" s="7"/>
       <c r="D835" s="8"/>
       <c r="G835" s="9"/>
       <c r="H835" s="6"/>
     </row>
-    <row r="836" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="836" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B836" s="7"/>
       <c r="D836" s="8"/>
       <c r="G836" s="9"/>
       <c r="H836" s="6"/>
     </row>
-    <row r="837" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="837" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B837" s="7"/>
       <c r="D837" s="8"/>
       <c r="G837" s="9"/>
       <c r="H837" s="6"/>
     </row>
-    <row r="838" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="838" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B838" s="7"/>
       <c r="D838" s="8"/>
       <c r="G838" s="9"/>
       <c r="H838" s="6"/>
     </row>
-    <row r="839" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="839" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B839" s="7"/>
       <c r="D839" s="8"/>
       <c r="G839" s="9"/>
       <c r="H839" s="6"/>
     </row>
-    <row r="840" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="840" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B840" s="7"/>
       <c r="D840" s="8"/>
       <c r="G840" s="9"/>
       <c r="H840" s="6"/>
     </row>
-    <row r="841" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="841" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B841" s="7"/>
       <c r="D841" s="8"/>
       <c r="G841" s="9"/>
       <c r="H841" s="6"/>
     </row>
-    <row r="842" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="842" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B842" s="7"/>
       <c r="D842" s="8"/>
       <c r="G842" s="9"/>
       <c r="H842" s="6"/>
     </row>
-    <row r="843" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="843" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B843" s="7"/>
       <c r="D843" s="8"/>
       <c r="G843" s="9"/>
       <c r="H843" s="6"/>
     </row>
-    <row r="844" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="844" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B844" s="7"/>
       <c r="D844" s="8"/>
       <c r="G844" s="9"/>
       <c r="H844" s="6"/>
     </row>
-    <row r="845" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="845" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B845" s="7"/>
       <c r="D845" s="8"/>
       <c r="G845" s="9"/>
       <c r="H845" s="6"/>
     </row>
-    <row r="846" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="846" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B846" s="7"/>
       <c r="D846" s="8"/>
       <c r="G846" s="9"/>
       <c r="H846" s="6"/>
     </row>
-    <row r="847" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="847" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B847" s="7"/>
       <c r="D847" s="8"/>
       <c r="G847" s="9"/>
       <c r="H847" s="6"/>
     </row>
-    <row r="848" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="848" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B848" s="7"/>
       <c r="D848" s="8"/>
       <c r="G848" s="9"/>
       <c r="H848" s="6"/>
     </row>
-    <row r="849" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="849" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B849" s="7"/>
       <c r="D849" s="8"/>
       <c r="G849" s="9"/>
       <c r="H849" s="6"/>
     </row>
-    <row r="850" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="850" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B850" s="7"/>
       <c r="D850" s="8"/>
       <c r="G850" s="9"/>
       <c r="H850" s="6"/>
     </row>
-    <row r="851" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="851" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B851" s="7"/>
       <c r="D851" s="8"/>
       <c r="G851" s="9"/>
       <c r="H851" s="6"/>
     </row>
-    <row r="852" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="852" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B852" s="7"/>
       <c r="D852" s="8"/>
       <c r="G852" s="9"/>
       <c r="H852" s="6"/>
     </row>
-    <row r="853" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="853" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B853" s="7"/>
       <c r="D853" s="8"/>
       <c r="G853" s="9"/>
       <c r="H853" s="6"/>
     </row>
-    <row r="854" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="854" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B854" s="7"/>
       <c r="D854" s="8"/>
       <c r="G854" s="9"/>
       <c r="H854" s="6"/>
     </row>
-    <row r="855" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="855" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B855" s="7"/>
       <c r="D855" s="8"/>
       <c r="G855" s="9"/>
       <c r="H855" s="6"/>
     </row>
-    <row r="856" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="856" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B856" s="7"/>
       <c r="D856" s="8"/>
       <c r="G856" s="9"/>
       <c r="H856" s="6"/>
     </row>
-    <row r="857" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="857" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B857" s="7"/>
       <c r="D857" s="8"/>
       <c r="G857" s="9"/>
       <c r="H857" s="6"/>
     </row>
-    <row r="858" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="858" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B858" s="7"/>
       <c r="D858" s="8"/>
       <c r="G858" s="9"/>
       <c r="H858" s="6"/>
     </row>
-    <row r="859" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="859" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B859" s="7"/>
       <c r="D859" s="8"/>
       <c r="G859" s="9"/>
       <c r="H859" s="6"/>
     </row>
-    <row r="860" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="860" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B860" s="7"/>
       <c r="D860" s="8"/>
       <c r="G860" s="9"/>
       <c r="H860" s="6"/>
     </row>
-    <row r="861" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="861" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B861" s="7"/>
       <c r="D861" s="8"/>
       <c r="G861" s="9"/>
       <c r="H861" s="6"/>
     </row>
-    <row r="862" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="862" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B862" s="7"/>
       <c r="D862" s="8"/>
       <c r="G862" s="9"/>
       <c r="H862" s="6"/>
     </row>
-    <row r="863" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="863" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B863" s="7"/>
       <c r="D863" s="8"/>
       <c r="G863" s="9"/>
       <c r="H863" s="6"/>
     </row>
-    <row r="864" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="864" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B864" s="7"/>
       <c r="D864" s="8"/>
       <c r="G864" s="9"/>
       <c r="H864" s="6"/>
     </row>
-    <row r="865" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="865" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B865" s="7"/>
       <c r="D865" s="8"/>
       <c r="G865" s="9"/>
       <c r="H865" s="6"/>
     </row>
-    <row r="866" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="866" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B866" s="7"/>
       <c r="D866" s="8"/>
       <c r="G866" s="9"/>
       <c r="H866" s="6"/>
     </row>
-    <row r="867" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="867" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B867" s="7"/>
       <c r="D867" s="8"/>
       <c r="G867" s="9"/>
       <c r="H867" s="6"/>
     </row>
-    <row r="868" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="868" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B868" s="7"/>
       <c r="D868" s="8"/>
       <c r="G868" s="9"/>
       <c r="H868" s="6"/>
     </row>
-    <row r="869" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="869" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B869" s="7"/>
       <c r="D869" s="8"/>
       <c r="G869" s="9"/>
       <c r="H869" s="6"/>
     </row>
-    <row r="870" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="870" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B870" s="7"/>
       <c r="D870" s="8"/>
       <c r="G870" s="9"/>
       <c r="H870" s="6"/>
     </row>
-    <row r="871" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="871" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B871" s="7"/>
       <c r="D871" s="8"/>
       <c r="G871" s="9"/>
       <c r="H871" s="6"/>
     </row>
-    <row r="872" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="872" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B872" s="7"/>
       <c r="D872" s="8"/>
       <c r="G872" s="9"/>
       <c r="H872" s="6"/>
     </row>
-    <row r="873" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="873" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B873" s="7"/>
       <c r="D873" s="8"/>
       <c r="G873" s="9"/>
       <c r="H873" s="6"/>
     </row>
-    <row r="874" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="874" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B874" s="7"/>
       <c r="D874" s="8"/>
       <c r="G874" s="9"/>
       <c r="H874" s="6"/>
     </row>
-    <row r="875" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="875" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B875" s="7"/>
       <c r="D875" s="8"/>
       <c r="G875" s="9"/>
       <c r="H875" s="6"/>
     </row>
-    <row r="876" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="876" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B876" s="7"/>
       <c r="D876" s="8"/>
       <c r="G876" s="9"/>
       <c r="H876" s="6"/>
     </row>
-    <row r="877" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="877" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B877" s="7"/>
       <c r="D877" s="8"/>
       <c r="G877" s="9"/>
       <c r="H877" s="6"/>
     </row>
-    <row r="878" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="878" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B878" s="7"/>
       <c r="D878" s="8"/>
       <c r="G878" s="9"/>
       <c r="H878" s="6"/>
     </row>
-    <row r="879" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="879" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B879" s="7"/>
       <c r="D879" s="8"/>
       <c r="G879" s="9"/>
       <c r="H879" s="6"/>
     </row>
-    <row r="880" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="880" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B880" s="7"/>
       <c r="D880" s="8"/>
       <c r="G880" s="9"/>
       <c r="H880" s="6"/>
     </row>
-    <row r="881" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="881" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B881" s="7"/>
       <c r="D881" s="8"/>
       <c r="G881" s="9"/>
       <c r="H881" s="6"/>
     </row>
-    <row r="882" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="882" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B882" s="7"/>
       <c r="D882" s="8"/>
       <c r="G882" s="9"/>
       <c r="H882" s="6"/>
     </row>
-    <row r="883" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="883" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B883" s="7"/>
       <c r="D883" s="8"/>
       <c r="G883" s="9"/>
       <c r="H883" s="6"/>
     </row>
-    <row r="884" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="884" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B884" s="7"/>
       <c r="D884" s="8"/>
       <c r="G884" s="9"/>
       <c r="H884" s="6"/>
     </row>
-    <row r="885" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="885" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B885" s="7"/>
       <c r="D885" s="8"/>
       <c r="G885" s="9"/>
       <c r="H885" s="6"/>
     </row>
-    <row r="886" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="886" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B886" s="7"/>
       <c r="D886" s="8"/>
       <c r="G886" s="9"/>
       <c r="H886" s="6"/>
     </row>
-    <row r="887" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="887" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B887" s="7"/>
       <c r="D887" s="8"/>
       <c r="G887" s="9"/>
       <c r="H887" s="6"/>
     </row>
-    <row r="888" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="888" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B888" s="7"/>
       <c r="D888" s="8"/>
       <c r="G888" s="9"/>
       <c r="H888" s="6"/>
     </row>
-    <row r="889" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="889" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B889" s="7"/>
       <c r="D889" s="8"/>
       <c r="G889" s="9"/>
       <c r="H889" s="6"/>
     </row>
-    <row r="890" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="890" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B890" s="7"/>
       <c r="D890" s="8"/>
       <c r="G890" s="9"/>
       <c r="H890" s="6"/>
     </row>
-    <row r="891" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="891" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B891" s="7"/>
       <c r="D891" s="8"/>
       <c r="G891" s="9"/>
       <c r="H891" s="6"/>
     </row>
-    <row r="892" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="892" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B892" s="7"/>
       <c r="D892" s="8"/>
       <c r="G892" s="9"/>
       <c r="H892" s="6"/>
     </row>
-    <row r="893" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="893" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B893" s="7"/>
       <c r="D893" s="8"/>
       <c r="G893" s="9"/>
       <c r="H893" s="6"/>
     </row>
-    <row r="894" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="894" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B894" s="7"/>
       <c r="D894" s="8"/>
       <c r="G894" s="9"/>
       <c r="H894" s="6"/>
     </row>
-    <row r="895" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="895" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B895" s="7"/>
       <c r="D895" s="8"/>
       <c r="G895" s="9"/>
       <c r="H895" s="6"/>
     </row>
-    <row r="896" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="896" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B896" s="7"/>
       <c r="D896" s="8"/>
       <c r="G896" s="9"/>
       <c r="H896" s="6"/>
     </row>
-    <row r="897" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="897" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B897" s="7"/>
       <c r="D897" s="8"/>
       <c r="G897" s="9"/>
       <c r="H897" s="6"/>
     </row>
-    <row r="898" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="898" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B898" s="7"/>
       <c r="D898" s="8"/>
       <c r="G898" s="9"/>
       <c r="H898" s="6"/>
     </row>
-    <row r="899" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="899" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B899" s="7"/>
       <c r="D899" s="8"/>
       <c r="G899" s="9"/>
       <c r="H899" s="6"/>
     </row>
-    <row r="900" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="900" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B900" s="7"/>
       <c r="D900" s="8"/>
       <c r="G900" s="9"/>
       <c r="H900" s="6"/>
     </row>
-    <row r="901" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="901" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B901" s="7"/>
       <c r="D901" s="8"/>
       <c r="G901" s="9"/>
       <c r="H901" s="6"/>
     </row>
-    <row r="902" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="902" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B902" s="7"/>
       <c r="D902" s="8"/>
       <c r="G902" s="9"/>
       <c r="H902" s="6"/>
     </row>
-    <row r="903" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="903" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B903" s="7"/>
       <c r="D903" s="8"/>
       <c r="G903" s="9"/>
       <c r="H903" s="6"/>
     </row>
-    <row r="904" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="904" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B904" s="7"/>
       <c r="D904" s="8"/>
       <c r="G904" s="9"/>
       <c r="H904" s="6"/>
     </row>
-    <row r="905" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="905" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B905" s="7"/>
       <c r="D905" s="8"/>
       <c r="G905" s="9"/>
       <c r="H905" s="6"/>
     </row>
-    <row r="906" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="906" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B906" s="7"/>
       <c r="D906" s="8"/>
       <c r="G906" s="9"/>
       <c r="H906" s="6"/>
     </row>
-    <row r="907" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="907" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B907" s="7"/>
       <c r="D907" s="8"/>
       <c r="G907" s="9"/>
       <c r="H907" s="6"/>
     </row>
-    <row r="908" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="908" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B908" s="7"/>
       <c r="D908" s="8"/>
       <c r="G908" s="9"/>
       <c r="H908" s="6"/>
     </row>
-    <row r="909" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="909" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B909" s="7"/>
       <c r="D909" s="8"/>
       <c r="G909" s="9"/>
       <c r="H909" s="6"/>
     </row>
-    <row r="910" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="910" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B910" s="7"/>
       <c r="D910" s="8"/>
       <c r="G910" s="9"/>
       <c r="H910" s="6"/>
     </row>
-    <row r="911" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="911" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B911" s="7"/>
       <c r="D911" s="8"/>
       <c r="G911" s="9"/>
       <c r="H911" s="6"/>
     </row>
-    <row r="912" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="912" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B912" s="7"/>
       <c r="D912" s="8"/>
       <c r="G912" s="9"/>
       <c r="H912" s="6"/>
     </row>
-    <row r="913" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="913" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B913" s="7"/>
       <c r="D913" s="8"/>
       <c r="G913" s="9"/>
       <c r="H913" s="6"/>
     </row>
-    <row r="914" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="914" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B914" s="7"/>
       <c r="D914" s="8"/>
       <c r="G914" s="9"/>
       <c r="H914" s="6"/>
     </row>
-    <row r="915" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="915" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B915" s="7"/>
       <c r="D915" s="8"/>
       <c r="G915" s="9"/>
       <c r="H915" s="6"/>
     </row>
-    <row r="916" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="916" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B916" s="7"/>
       <c r="D916" s="8"/>
       <c r="G916" s="9"/>
       <c r="H916" s="6"/>
     </row>
-    <row r="917" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="917" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B917" s="7"/>
       <c r="D917" s="8"/>
       <c r="G917" s="9"/>
       <c r="H917" s="6"/>
     </row>
-    <row r="918" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="918" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B918" s="7"/>
       <c r="D918" s="8"/>
       <c r="G918" s="9"/>
       <c r="H918" s="6"/>
     </row>
-    <row r="919" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="919" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B919" s="7"/>
       <c r="D919" s="8"/>
       <c r="G919" s="9"/>
       <c r="H919" s="6"/>
     </row>
-    <row r="920" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="920" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B920" s="7"/>
       <c r="D920" s="8"/>
       <c r="G920" s="9"/>
       <c r="H920" s="6"/>
     </row>
-    <row r="921" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="921" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B921" s="7"/>
       <c r="D921" s="8"/>
       <c r="G921" s="9"/>
       <c r="H921" s="6"/>
     </row>
-    <row r="922" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="922" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B922" s="7"/>
       <c r="D922" s="8"/>
       <c r="G922" s="9"/>
       <c r="H922" s="6"/>
     </row>
-    <row r="923" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="923" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B923" s="7"/>
       <c r="D923" s="8"/>
       <c r="G923" s="9"/>
       <c r="H923" s="6"/>
     </row>
-    <row r="924" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="924" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B924" s="7"/>
       <c r="D924" s="8"/>
       <c r="G924" s="9"/>
       <c r="H924" s="6"/>
     </row>
-    <row r="925" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="925" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B925" s="7"/>
       <c r="D925" s="8"/>
       <c r="G925" s="9"/>
       <c r="H925" s="6"/>
     </row>
-    <row r="926" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="926" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B926" s="7"/>
       <c r="D926" s="8"/>
       <c r="G926" s="9"/>
       <c r="H926" s="6"/>
     </row>
-    <row r="927" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="927" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B927" s="7"/>
       <c r="D927" s="8"/>
       <c r="G927" s="9"/>
       <c r="H927" s="6"/>
     </row>
-    <row r="928" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="928" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B928" s="7"/>
       <c r="D928" s="8"/>
       <c r="G928" s="9"/>
       <c r="H928" s="6"/>
     </row>
-    <row r="929" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="929" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B929" s="7"/>
       <c r="D929" s="8"/>
       <c r="G929" s="9"/>
       <c r="H929" s="6"/>
     </row>
-    <row r="930" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="930" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B930" s="7"/>
       <c r="D930" s="8"/>
       <c r="G930" s="9"/>
       <c r="H930" s="6"/>
     </row>
-    <row r="931" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="931" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B931" s="7"/>
       <c r="D931" s="8"/>
       <c r="G931" s="9"/>
       <c r="H931" s="6"/>
     </row>
-    <row r="932" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="932" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B932" s="7"/>
       <c r="D932" s="8"/>
       <c r="G932" s="9"/>
       <c r="H932" s="6"/>
     </row>
-    <row r="933" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="933" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B933" s="7"/>
       <c r="D933" s="8"/>
       <c r="G933" s="9"/>
       <c r="H933" s="6"/>
     </row>
-    <row r="934" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="934" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B934" s="7"/>
       <c r="D934" s="8"/>
       <c r="G934" s="9"/>
       <c r="H934" s="6"/>
     </row>
-    <row r="935" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="935" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B935" s="7"/>
       <c r="D935" s="8"/>
       <c r="G935" s="9"/>
       <c r="H935" s="6"/>
     </row>
-    <row r="936" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="936" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B936" s="7"/>
       <c r="D936" s="8"/>
       <c r="G936" s="9"/>
       <c r="H936" s="6"/>
     </row>
-    <row r="937" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="937" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B937" s="7"/>
       <c r="D937" s="8"/>
       <c r="G937" s="9"/>
       <c r="H937" s="6"/>
     </row>
-    <row r="938" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="938" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B938" s="7"/>
       <c r="D938" s="8"/>
       <c r="G938" s="9"/>
       <c r="H938" s="6"/>
     </row>
-    <row r="939" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="939" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B939" s="7"/>
       <c r="D939" s="8"/>
       <c r="G939" s="9"/>
       <c r="H939" s="6"/>
     </row>
-    <row r="940" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="940" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B940" s="7"/>
       <c r="D940" s="8"/>
       <c r="G940" s="9"/>
       <c r="H940" s="6"/>
     </row>
-    <row r="941" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="941" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B941" s="7"/>
       <c r="D941" s="8"/>
       <c r="G941" s="9"/>
       <c r="H941" s="6"/>
     </row>
-    <row r="942" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="942" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B942" s="7"/>
       <c r="D942" s="8"/>
       <c r="G942" s="9"/>
       <c r="H942" s="6"/>
     </row>
-    <row r="943" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="943" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B943" s="7"/>
       <c r="D943" s="8"/>
       <c r="G943" s="9"/>
       <c r="H943" s="6"/>
     </row>
-    <row r="944" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="944" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B944" s="7"/>
       <c r="D944" s="8"/>
       <c r="G944" s="9"/>
       <c r="H944" s="6"/>
     </row>
-    <row r="945" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="945" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B945" s="7"/>
       <c r="D945" s="8"/>
       <c r="G945" s="9"/>
       <c r="H945" s="6"/>
     </row>
-    <row r="946" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="946" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B946" s="7"/>
       <c r="D946" s="8"/>
       <c r="G946" s="9"/>
       <c r="H946" s="6"/>
     </row>
-    <row r="947" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="947" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B947" s="7"/>
       <c r="D947" s="8"/>
       <c r="G947" s="9"/>
       <c r="H947" s="6"/>
     </row>
-    <row r="948" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="948" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B948" s="7"/>
       <c r="D948" s="8"/>
       <c r="G948" s="9"/>
       <c r="H948" s="6"/>
     </row>
-    <row r="949" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="949" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B949" s="7"/>
       <c r="D949" s="8"/>
       <c r="G949" s="9"/>
       <c r="H949" s="6"/>
     </row>
-    <row r="950" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="950" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B950" s="7"/>
       <c r="D950" s="8"/>
       <c r="G950" s="9"/>
       <c r="H950" s="6"/>
     </row>
-    <row r="951" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="951" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B951" s="7"/>
       <c r="D951" s="8"/>
       <c r="G951" s="9"/>
       <c r="H951" s="6"/>
     </row>
-    <row r="952" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="952" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B952" s="7"/>
       <c r="D952" s="8"/>
       <c r="G952" s="9"/>
       <c r="H952" s="6"/>
     </row>
-    <row r="953" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="953" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B953" s="7"/>
       <c r="D953" s="8"/>
       <c r="G953" s="9"/>
       <c r="H953" s="6"/>
     </row>
-    <row r="954" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="954" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B954" s="7"/>
       <c r="D954" s="8"/>
       <c r="G954" s="9"/>
       <c r="H954" s="6"/>
     </row>
-    <row r="955" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="955" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B955" s="7"/>
       <c r="D955" s="8"/>
       <c r="G955" s="9"/>
       <c r="H955" s="6"/>
     </row>
-    <row r="956" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="956" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B956" s="7"/>
       <c r="D956" s="8"/>
       <c r="G956" s="9"/>
       <c r="H956" s="6"/>
     </row>
-    <row r="957" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="957" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B957" s="7"/>
       <c r="D957" s="8"/>
       <c r="G957" s="9"/>
       <c r="H957" s="6"/>
     </row>
-    <row r="958" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="958" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B958" s="7"/>
       <c r="D958" s="8"/>
       <c r="G958" s="9"/>
       <c r="H958" s="6"/>
     </row>
-    <row r="959" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="959" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B959" s="7"/>
       <c r="D959" s="8"/>
       <c r="G959" s="9"/>
       <c r="H959" s="6"/>
     </row>
-    <row r="960" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="960" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B960" s="7"/>
       <c r="D960" s="8"/>
       <c r="G960" s="9"/>
       <c r="H960" s="6"/>
     </row>
-    <row r="961" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="961" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B961" s="7"/>
       <c r="D961" s="8"/>
       <c r="G961" s="9"/>
       <c r="H961" s="6"/>
     </row>
-    <row r="962" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="962" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B962" s="7"/>
       <c r="D962" s="8"/>
       <c r="G962" s="9"/>
       <c r="H962" s="6"/>
     </row>
-    <row r="963" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="963" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B963" s="7"/>
       <c r="D963" s="8"/>
       <c r="G963" s="9"/>
       <c r="H963" s="6"/>
     </row>
-    <row r="964" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="964" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B964" s="7"/>
       <c r="D964" s="8"/>
       <c r="G964" s="9"/>
       <c r="H964" s="6"/>
     </row>
-    <row r="965" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="965" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B965" s="7"/>
       <c r="D965" s="8"/>
       <c r="G965" s="9"/>
       <c r="H965" s="6"/>
     </row>
-    <row r="966" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="966" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B966" s="7"/>
       <c r="D966" s="8"/>
       <c r="G966" s="9"/>
       <c r="H966" s="6"/>
     </row>
-    <row r="967" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="967" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B967" s="7"/>
       <c r="D967" s="8"/>
       <c r="G967" s="9"/>
       <c r="H967" s="6"/>
     </row>
-    <row r="968" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="968" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B968" s="7"/>
       <c r="D968" s="8"/>
       <c r="G968" s="9"/>
       <c r="H968" s="6"/>
     </row>
-    <row r="969" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="969" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B969" s="7"/>
       <c r="D969" s="8"/>
       <c r="G969" s="9"/>
       <c r="H969" s="6"/>
     </row>
-    <row r="970" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="970" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B970" s="7"/>
       <c r="D970" s="8"/>
       <c r="G970" s="9"/>
       <c r="H970" s="6"/>
     </row>
-    <row r="971" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="971" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B971" s="7"/>
       <c r="D971" s="8"/>
       <c r="G971" s="9"/>
       <c r="H971" s="6"/>
     </row>
-    <row r="972" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="972" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B972" s="7"/>
       <c r="D972" s="8"/>
       <c r="G972" s="9"/>
       <c r="H972" s="6"/>
     </row>
-    <row r="973" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="973" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B973" s="7"/>
       <c r="D973" s="8"/>
       <c r="G973" s="9"/>
       <c r="H973" s="6"/>
     </row>
-    <row r="974" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="974" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B974" s="7"/>
       <c r="D974" s="8"/>
       <c r="G974" s="9"/>
       <c r="H974" s="6"/>
     </row>
-    <row r="975" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="975" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B975" s="7"/>
       <c r="D975" s="8"/>
       <c r="G975" s="9"/>
       <c r="H975" s="6"/>
     </row>
-    <row r="976" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="976" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B976" s="7"/>
       <c r="D976" s="8"/>
       <c r="G976" s="9"/>
       <c r="H976" s="6"/>
     </row>
-    <row r="977" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="977" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B977" s="7"/>
       <c r="D977" s="8"/>
       <c r="G977" s="9"/>
       <c r="H977" s="6"/>
     </row>
-    <row r="978" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="978" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B978" s="7"/>
       <c r="D978" s="8"/>
       <c r="G978" s="9"/>
       <c r="H978" s="6"/>
     </row>
-    <row r="979" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="979" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B979" s="7"/>
       <c r="D979" s="8"/>
       <c r="G979" s="9"/>
       <c r="H979" s="6"/>
     </row>
-    <row r="980" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="980" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B980" s="7"/>
       <c r="D980" s="8"/>
       <c r="G980" s="9"/>
       <c r="H980" s="6"/>
     </row>
-    <row r="981" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="981" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B981" s="7"/>
       <c r="D981" s="8"/>
       <c r="G981" s="9"/>
       <c r="H981" s="6"/>
     </row>
-    <row r="982" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="982" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B982" s="7"/>
       <c r="D982" s="8"/>
       <c r="G982" s="9"/>
       <c r="H982" s="6"/>
     </row>
-    <row r="983" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="983" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B983" s="7"/>
       <c r="D983" s="8"/>
       <c r="G983" s="9"/>
       <c r="H983" s="6"/>
     </row>
-    <row r="984" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="984" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B984" s="7"/>
       <c r="D984" s="8"/>
       <c r="G984" s="9"/>
       <c r="H984" s="6"/>
     </row>
-    <row r="985" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="985" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B985" s="7"/>
       <c r="D985" s="8"/>
       <c r="G985" s="9"/>
       <c r="H985" s="6"/>
     </row>
-    <row r="986" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="986" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B986" s="7"/>
       <c r="D986" s="8"/>
       <c r="G986" s="9"/>
       <c r="H986" s="6"/>
     </row>
-    <row r="987" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="987" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B987" s="7"/>
       <c r="D987" s="8"/>
       <c r="G987" s="9"/>
       <c r="H987" s="6"/>
     </row>
-    <row r="988" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="988" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B988" s="7"/>
       <c r="D988" s="8"/>
       <c r="G988" s="9"/>
       <c r="H988" s="6"/>
     </row>
-    <row r="989" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="989" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B989" s="7"/>
       <c r="D989" s="8"/>
       <c r="G989" s="9"/>
       <c r="H989" s="6"/>
     </row>
-    <row r="990" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="990" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B990" s="7"/>
       <c r="D990" s="8"/>
       <c r="G990" s="9"/>
       <c r="H990" s="6"/>
     </row>
-    <row r="991" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="991" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B991" s="7"/>
       <c r="D991" s="8"/>
       <c r="G991" s="9"/>
       <c r="H991" s="6"/>
     </row>
-    <row r="992" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="992" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B992" s="7"/>
       <c r="D992" s="8"/>
       <c r="G992" s="9"/>
       <c r="H992" s="6"/>
     </row>
-    <row r="993" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="993" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B993" s="7"/>
       <c r="D993" s="8"/>
       <c r="G993" s="9"/>
       <c r="H993" s="6"/>
     </row>
-    <row r="994" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="994" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B994" s="7"/>
       <c r="D994" s="8"/>
       <c r="G994" s="9"/>
       <c r="H994" s="6"/>
     </row>
-    <row r="995" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="995" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B995" s="7"/>
       <c r="D995" s="8"/>
       <c r="G995" s="9"/>
       <c r="H995" s="6"/>
     </row>
-    <row r="996" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="996" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B996" s="7"/>
       <c r="D996" s="8"/>
       <c r="G996" s="9"/>
       <c r="H996" s="6"/>
     </row>
-    <row r="997" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="997" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B997" s="7"/>
       <c r="D997" s="8"/>
       <c r="G997" s="9"/>
       <c r="H997" s="6"/>
     </row>
-    <row r="998" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="998" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B998" s="7"/>
       <c r="D998" s="8"/>
       <c r="G998" s="9"/>
       <c r="H998" s="6"/>
     </row>
-    <row r="999" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="999" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B999" s="7"/>
       <c r="D999" s="8"/>
       <c r="G999" s="9"/>
       <c r="H999" s="6"/>
     </row>
-    <row r="1000" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1000" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B1000" s="7"/>
       <c r="D1000" s="8"/>
       <c r="G1000" s="9"/>
